--- a/output/version3/test/25-15/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1105</v>
+        <v>1084</v>
       </c>
       <c r="C2" t="n">
-        <v>1223</v>
+        <v>1127</v>
       </c>
       <c r="D2" t="n">
-        <v>1015</v>
+        <v>1086</v>
       </c>
       <c r="E2" t="n">
-        <v>1094</v>
+        <v>990</v>
       </c>
       <c r="F2" t="n">
-        <v>1170</v>
+        <v>1075</v>
       </c>
       <c r="G2" t="n">
-        <v>1010</v>
+        <v>1222</v>
       </c>
       <c r="H2" t="n">
-        <v>1082</v>
+        <v>1181</v>
       </c>
       <c r="I2" t="n">
-        <v>1209</v>
+        <v>1224</v>
       </c>
       <c r="J2" t="n">
-        <v>1139</v>
+        <v>1098</v>
       </c>
       <c r="K2" t="n">
-        <v>1051</v>
+        <v>1085</v>
       </c>
       <c r="L2" t="n">
-        <v>1109.8</v>
+        <v>1117.2</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1076</v>
+        <v>1059</v>
       </c>
       <c r="C3" t="n">
-        <v>1050</v>
+        <v>927</v>
       </c>
       <c r="D3" t="n">
-        <v>1094</v>
+        <v>1234</v>
       </c>
       <c r="E3" t="n">
-        <v>1315</v>
+        <v>1134</v>
       </c>
       <c r="F3" t="n">
-        <v>1099</v>
+        <v>1045</v>
       </c>
       <c r="G3" t="n">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="H3" t="n">
-        <v>1314</v>
+        <v>1004</v>
       </c>
       <c r="I3" t="n">
-        <v>1069</v>
+        <v>1114</v>
       </c>
       <c r="J3" t="n">
-        <v>1167</v>
+        <v>1029</v>
       </c>
       <c r="K3" t="n">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="L3" t="n">
-        <v>1132.8</v>
+        <v>1067.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1095</v>
+        <v>1150</v>
       </c>
       <c r="C4" t="n">
-        <v>1228</v>
+        <v>1081</v>
       </c>
       <c r="D4" t="n">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="E4" t="n">
-        <v>1327</v>
+        <v>1138</v>
       </c>
       <c r="F4" t="n">
-        <v>1017</v>
+        <v>975</v>
       </c>
       <c r="G4" t="n">
-        <v>949</v>
+        <v>983</v>
       </c>
       <c r="H4" t="n">
-        <v>989</v>
+        <v>1098</v>
       </c>
       <c r="I4" t="n">
-        <v>1252</v>
+        <v>1119</v>
       </c>
       <c r="J4" t="n">
-        <v>1268</v>
+        <v>994</v>
       </c>
       <c r="K4" t="n">
-        <v>1006</v>
+        <v>1075</v>
       </c>
       <c r="L4" t="n">
-        <v>1123.3</v>
+        <v>1071.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="C5" t="n">
-        <v>951</v>
+        <v>997</v>
       </c>
       <c r="D5" t="n">
-        <v>943</v>
+        <v>1005</v>
       </c>
       <c r="E5" t="n">
-        <v>1016</v>
+        <v>912</v>
       </c>
       <c r="F5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>936</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1048</v>
+      </c>
+      <c r="I5" t="n">
         <v>895</v>
       </c>
-      <c r="G5" t="n">
-        <v>959</v>
-      </c>
-      <c r="H5" t="n">
-        <v>927</v>
-      </c>
-      <c r="I5" t="n">
-        <v>965</v>
-      </c>
       <c r="J5" t="n">
-        <v>916</v>
+        <v>1136</v>
       </c>
       <c r="K5" t="n">
-        <v>1052</v>
+        <v>1087</v>
       </c>
       <c r="L5" t="n">
-        <v>960.3</v>
+        <v>1018.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1266</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>1180</v>
+        <v>1086</v>
       </c>
       <c r="D6" t="n">
-        <v>1032</v>
+        <v>1166</v>
       </c>
       <c r="E6" t="n">
-        <v>1137</v>
+        <v>1016</v>
       </c>
       <c r="F6" t="n">
-        <v>1152</v>
+        <v>1047</v>
       </c>
       <c r="G6" t="n">
-        <v>1192</v>
+        <v>983</v>
       </c>
       <c r="H6" t="n">
-        <v>1112</v>
+        <v>1071</v>
       </c>
       <c r="I6" t="n">
-        <v>1129</v>
+        <v>1063</v>
       </c>
       <c r="J6" t="n">
-        <v>1108</v>
+        <v>986</v>
       </c>
       <c r="K6" t="n">
-        <v>1155</v>
+        <v>1271</v>
       </c>
       <c r="L6" t="n">
-        <v>1146.3</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1018</v>
+        <v>978</v>
       </c>
       <c r="C7" t="n">
-        <v>1067</v>
+        <v>945</v>
       </c>
       <c r="D7" t="n">
-        <v>926</v>
+        <v>1016</v>
       </c>
       <c r="E7" t="n">
-        <v>896</v>
+        <v>1169</v>
       </c>
       <c r="F7" t="n">
-        <v>1074</v>
+        <v>1038</v>
       </c>
       <c r="G7" t="n">
-        <v>900</v>
+        <v>1090</v>
       </c>
       <c r="H7" t="n">
-        <v>1045</v>
+        <v>866</v>
       </c>
       <c r="I7" t="n">
-        <v>932</v>
+        <v>1183</v>
       </c>
       <c r="J7" t="n">
-        <v>1032</v>
+        <v>1165</v>
       </c>
       <c r="K7" t="n">
-        <v>1099</v>
+        <v>868</v>
       </c>
       <c r="L7" t="n">
-        <v>998.9</v>
+        <v>1031.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1122</v>
+        <v>1079</v>
       </c>
       <c r="C8" t="n">
-        <v>1030</v>
+        <v>1087</v>
       </c>
       <c r="D8" t="n">
-        <v>1059</v>
+        <v>1150</v>
       </c>
       <c r="E8" t="n">
-        <v>1046</v>
+        <v>992</v>
       </c>
       <c r="F8" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G8" t="n">
+        <v>931</v>
+      </c>
+      <c r="H8" t="n">
         <v>1119</v>
       </c>
-      <c r="G8" t="n">
-        <v>1013</v>
-      </c>
-      <c r="H8" t="n">
-        <v>949</v>
-      </c>
       <c r="I8" t="n">
-        <v>1072</v>
+        <v>966</v>
       </c>
       <c r="J8" t="n">
-        <v>1067</v>
+        <v>1202</v>
       </c>
       <c r="K8" t="n">
-        <v>1004</v>
+        <v>1279</v>
       </c>
       <c r="L8" t="n">
-        <v>1048.1</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>977</v>
+        <v>922</v>
       </c>
       <c r="C9" t="n">
-        <v>1020</v>
+        <v>891</v>
       </c>
       <c r="D9" t="n">
-        <v>913</v>
+        <v>982</v>
       </c>
       <c r="E9" t="n">
-        <v>915</v>
+        <v>1148</v>
       </c>
       <c r="F9" t="n">
-        <v>1066</v>
+        <v>946</v>
       </c>
       <c r="G9" t="n">
-        <v>1084</v>
+        <v>1175</v>
       </c>
       <c r="H9" t="n">
-        <v>1021</v>
+        <v>849</v>
       </c>
       <c r="I9" t="n">
-        <v>914</v>
+        <v>957</v>
       </c>
       <c r="J9" t="n">
-        <v>990</v>
+        <v>1124</v>
       </c>
       <c r="K9" t="n">
-        <v>1119</v>
+        <v>958</v>
       </c>
       <c r="L9" t="n">
-        <v>1001.9</v>
+        <v>995.2</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1174</v>
+        <v>1078</v>
       </c>
       <c r="C10" t="n">
-        <v>1123</v>
+        <v>1190</v>
       </c>
       <c r="D10" t="n">
-        <v>1192</v>
+        <v>1164</v>
       </c>
       <c r="E10" t="n">
-        <v>1142</v>
+        <v>1002</v>
       </c>
       <c r="F10" t="n">
-        <v>1191</v>
+        <v>1049</v>
       </c>
       <c r="G10" t="n">
-        <v>973</v>
+        <v>1002</v>
       </c>
       <c r="H10" t="n">
-        <v>1170</v>
+        <v>971</v>
       </c>
       <c r="I10" t="n">
-        <v>1162</v>
+        <v>912</v>
       </c>
       <c r="J10" t="n">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="K10" t="n">
-        <v>1126</v>
+        <v>1048</v>
       </c>
       <c r="L10" t="n">
-        <v>1132.7</v>
+        <v>1050.2</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1106</v>
+        <v>1225</v>
       </c>
       <c r="C11" t="n">
-        <v>1146</v>
+        <v>1093</v>
       </c>
       <c r="D11" t="n">
-        <v>1075</v>
+        <v>1238</v>
       </c>
       <c r="E11" t="n">
-        <v>1123</v>
+        <v>1288</v>
       </c>
       <c r="F11" t="n">
-        <v>921</v>
+        <v>1119</v>
       </c>
       <c r="G11" t="n">
-        <v>1023</v>
+        <v>1175</v>
       </c>
       <c r="H11" t="n">
-        <v>1069</v>
+        <v>1200</v>
       </c>
       <c r="I11" t="n">
-        <v>1065</v>
+        <v>1160</v>
       </c>
       <c r="J11" t="n">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="K11" t="n">
-        <v>1198</v>
+        <v>1032</v>
       </c>
       <c r="L11" t="n">
-        <v>1070.7</v>
+        <v>1151.7</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1191</v>
+        <v>1326</v>
       </c>
       <c r="C12" t="n">
-        <v>1142</v>
+        <v>1398</v>
       </c>
       <c r="D12" t="n">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="E12" t="n">
-        <v>1084</v>
+        <v>1323</v>
       </c>
       <c r="F12" t="n">
-        <v>1264</v>
+        <v>1123</v>
       </c>
       <c r="G12" t="n">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="H12" t="n">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="I12" t="n">
-        <v>931</v>
+        <v>1137</v>
       </c>
       <c r="J12" t="n">
-        <v>1162</v>
+        <v>1152</v>
       </c>
       <c r="K12" t="n">
-        <v>1022</v>
+        <v>1042</v>
       </c>
       <c r="L12" t="n">
-        <v>1103.2</v>
+        <v>1175.4</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1241</v>
+        <v>1181</v>
       </c>
       <c r="C13" t="n">
-        <v>1110</v>
+        <v>1097</v>
       </c>
       <c r="D13" t="n">
-        <v>1236</v>
+        <v>1174</v>
       </c>
       <c r="E13" t="n">
-        <v>1010</v>
+        <v>1227</v>
       </c>
       <c r="F13" t="n">
-        <v>1269</v>
+        <v>1067</v>
       </c>
       <c r="G13" t="n">
-        <v>1282</v>
+        <v>1250</v>
       </c>
       <c r="H13" t="n">
-        <v>1338</v>
+        <v>1169</v>
       </c>
       <c r="I13" t="n">
-        <v>1261</v>
+        <v>1425</v>
       </c>
       <c r="J13" t="n">
-        <v>1213</v>
+        <v>1203</v>
       </c>
       <c r="K13" t="n">
-        <v>1257</v>
+        <v>1268</v>
       </c>
       <c r="L13" t="n">
-        <v>1221.7</v>
+        <v>1206.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>970</v>
+        <v>1059</v>
       </c>
       <c r="C14" t="n">
-        <v>904</v>
+        <v>944</v>
       </c>
       <c r="D14" t="n">
-        <v>1203</v>
+        <v>986</v>
       </c>
       <c r="E14" t="n">
-        <v>971</v>
+        <v>1235</v>
       </c>
       <c r="F14" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G14" t="n">
         <v>947</v>
       </c>
-      <c r="G14" t="n">
-        <v>946</v>
-      </c>
       <c r="H14" t="n">
-        <v>1090</v>
+        <v>1126</v>
       </c>
       <c r="I14" t="n">
-        <v>945</v>
+        <v>1289</v>
       </c>
       <c r="J14" t="n">
-        <v>1142</v>
+        <v>1074</v>
       </c>
       <c r="K14" t="n">
-        <v>918</v>
+        <v>1051</v>
       </c>
       <c r="L14" t="n">
-        <v>1003.6</v>
+        <v>1094.6</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1122</v>
+        <v>993</v>
       </c>
       <c r="C15" t="n">
-        <v>1235</v>
+        <v>1061</v>
       </c>
       <c r="D15" t="n">
-        <v>1249</v>
+        <v>1071</v>
       </c>
       <c r="E15" t="n">
-        <v>1048</v>
+        <v>1193</v>
       </c>
       <c r="F15" t="n">
-        <v>1164</v>
+        <v>998</v>
       </c>
       <c r="G15" t="n">
-        <v>1072</v>
+        <v>1162</v>
       </c>
       <c r="H15" t="n">
-        <v>1030</v>
+        <v>1192</v>
       </c>
       <c r="I15" t="n">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="J15" t="n">
-        <v>988</v>
+        <v>1089</v>
       </c>
       <c r="K15" t="n">
-        <v>1089</v>
+        <v>1263</v>
       </c>
       <c r="L15" t="n">
-        <v>1112</v>
+        <v>1114.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1052</v>
+        <v>903</v>
       </c>
       <c r="C16" t="n">
-        <v>1071</v>
+        <v>1177</v>
       </c>
       <c r="D16" t="n">
-        <v>1209</v>
+        <v>1125</v>
       </c>
       <c r="E16" t="n">
-        <v>994</v>
+        <v>1176</v>
       </c>
       <c r="F16" t="n">
-        <v>1302</v>
+        <v>1233</v>
       </c>
       <c r="G16" t="n">
-        <v>1065</v>
+        <v>1016</v>
       </c>
       <c r="H16" t="n">
-        <v>1232</v>
+        <v>1167</v>
       </c>
       <c r="I16" t="n">
-        <v>1055</v>
+        <v>1216</v>
       </c>
       <c r="J16" t="n">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="K16" t="n">
-        <v>999</v>
+        <v>1042</v>
       </c>
       <c r="L16" t="n">
-        <v>1099.1</v>
+        <v>1107.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1114</v>
+        <v>1036</v>
       </c>
       <c r="C17" t="n">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="D17" t="n">
-        <v>1054</v>
+        <v>1097</v>
       </c>
       <c r="E17" t="n">
-        <v>1131</v>
+        <v>1141</v>
       </c>
       <c r="F17" t="n">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="G17" t="n">
-        <v>1004</v>
+        <v>1155</v>
       </c>
       <c r="H17" t="n">
-        <v>1075</v>
+        <v>1159</v>
       </c>
       <c r="I17" t="n">
-        <v>1066</v>
+        <v>1109</v>
       </c>
       <c r="J17" t="n">
-        <v>1101</v>
+        <v>1123</v>
       </c>
       <c r="K17" t="n">
-        <v>1207</v>
+        <v>1163</v>
       </c>
       <c r="L17" t="n">
-        <v>1080.2</v>
+        <v>1103.3</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1133</v>
+        <v>1222</v>
       </c>
       <c r="C18" t="n">
-        <v>1197</v>
+        <v>1306</v>
       </c>
       <c r="D18" t="n">
-        <v>1017</v>
+        <v>996</v>
       </c>
       <c r="E18" t="n">
-        <v>1041</v>
+        <v>1185</v>
       </c>
       <c r="F18" t="n">
-        <v>1037</v>
+        <v>1120</v>
       </c>
       <c r="G18" t="n">
-        <v>1308</v>
+        <v>1291</v>
       </c>
       <c r="H18" t="n">
-        <v>1253</v>
+        <v>1067</v>
       </c>
       <c r="I18" t="n">
-        <v>1136</v>
+        <v>984</v>
       </c>
       <c r="J18" t="n">
-        <v>1032</v>
+        <v>973</v>
       </c>
       <c r="K18" t="n">
-        <v>1265</v>
+        <v>1052</v>
       </c>
       <c r="L18" t="n">
-        <v>1141.9</v>
+        <v>1119.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1120</v>
+        <v>1036</v>
       </c>
       <c r="C19" t="n">
-        <v>1099</v>
+        <v>1130</v>
       </c>
       <c r="D19" t="n">
-        <v>1095</v>
+        <v>1273</v>
       </c>
       <c r="E19" t="n">
-        <v>1081</v>
+        <v>1064</v>
       </c>
       <c r="F19" t="n">
-        <v>1251</v>
+        <v>1179</v>
       </c>
       <c r="G19" t="n">
-        <v>1307</v>
+        <v>1153</v>
       </c>
       <c r="H19" t="n">
-        <v>1161</v>
+        <v>1265</v>
       </c>
       <c r="I19" t="n">
-        <v>1085</v>
+        <v>1062</v>
       </c>
       <c r="J19" t="n">
-        <v>1138</v>
+        <v>1160</v>
       </c>
       <c r="K19" t="n">
-        <v>1069</v>
+        <v>1107</v>
       </c>
       <c r="L19" t="n">
-        <v>1140.6</v>
+        <v>1142.9</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
+        <v>1061</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1086</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1102</v>
+      </c>
+      <c r="F20" t="n">
         <v>1125</v>
       </c>
-      <c r="C20" t="n">
-        <v>1090</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1115</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1251</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1267</v>
-      </c>
       <c r="G20" t="n">
-        <v>1221</v>
+        <v>1037</v>
       </c>
       <c r="H20" t="n">
-        <v>1052</v>
+        <v>1142</v>
       </c>
       <c r="I20" t="n">
-        <v>1026</v>
+        <v>1120</v>
       </c>
       <c r="J20" t="n">
-        <v>1273</v>
+        <v>1099</v>
       </c>
       <c r="K20" t="n">
-        <v>1092</v>
+        <v>1275</v>
       </c>
       <c r="L20" t="n">
-        <v>1151.2</v>
+        <v>1104.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1158</v>
+        <v>1134</v>
       </c>
       <c r="C21" t="n">
-        <v>1114</v>
+        <v>1297</v>
       </c>
       <c r="D21" t="n">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="E21" t="n">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="F21" t="n">
-        <v>1080</v>
+        <v>1008</v>
       </c>
       <c r="G21" t="n">
-        <v>1136</v>
+        <v>1222</v>
       </c>
       <c r="H21" t="n">
-        <v>1218</v>
+        <v>1074</v>
       </c>
       <c r="I21" t="n">
-        <v>1073</v>
+        <v>1221</v>
       </c>
       <c r="J21" t="n">
-        <v>1282</v>
+        <v>1165</v>
       </c>
       <c r="K21" t="n">
-        <v>1251</v>
+        <v>1180</v>
       </c>
       <c r="L21" t="n">
-        <v>1148.9</v>
+        <v>1147.8</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="C22" t="n">
-        <v>1231</v>
+        <v>1175</v>
       </c>
       <c r="D22" t="n">
-        <v>1225</v>
+        <v>1090</v>
       </c>
       <c r="E22" t="n">
-        <v>1353</v>
+        <v>1119</v>
       </c>
       <c r="F22" t="n">
-        <v>1337</v>
+        <v>1051</v>
       </c>
       <c r="G22" t="n">
-        <v>1194</v>
+        <v>1293</v>
       </c>
       <c r="H22" t="n">
-        <v>1126</v>
+        <v>1109</v>
       </c>
       <c r="I22" t="n">
-        <v>1046</v>
+        <v>1110</v>
       </c>
       <c r="J22" t="n">
-        <v>1325</v>
+        <v>1201</v>
       </c>
       <c r="K22" t="n">
-        <v>1186</v>
+        <v>1132</v>
       </c>
       <c r="L22" t="n">
-        <v>1213.6</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1030</v>
+        <v>1076</v>
       </c>
       <c r="C23" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D23" t="n">
         <v>989</v>
       </c>
-      <c r="D23" t="n">
-        <v>1038</v>
-      </c>
       <c r="E23" t="n">
-        <v>1335</v>
+        <v>1027</v>
       </c>
       <c r="F23" t="n">
-        <v>952</v>
+        <v>1013</v>
       </c>
       <c r="G23" t="n">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="H23" t="n">
-        <v>997</v>
+        <v>1073</v>
       </c>
       <c r="I23" t="n">
-        <v>946</v>
+        <v>1112</v>
       </c>
       <c r="J23" t="n">
-        <v>1141</v>
+        <v>1051</v>
       </c>
       <c r="K23" t="n">
-        <v>999</v>
+        <v>1233</v>
       </c>
       <c r="L23" t="n">
-        <v>1044.1</v>
+        <v>1076.1</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1133</v>
+        <v>1164</v>
       </c>
       <c r="C24" t="n">
-        <v>1093</v>
+        <v>1267</v>
       </c>
       <c r="D24" t="n">
-        <v>1049</v>
+        <v>1091</v>
       </c>
       <c r="E24" t="n">
-        <v>1000</v>
+        <v>1045</v>
       </c>
       <c r="F24" t="n">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="G24" t="n">
-        <v>1154</v>
+        <v>1006</v>
       </c>
       <c r="H24" t="n">
-        <v>981</v>
+        <v>1319</v>
       </c>
       <c r="I24" t="n">
-        <v>1173</v>
+        <v>1043</v>
       </c>
       <c r="J24" t="n">
-        <v>1029</v>
+        <v>1116</v>
       </c>
       <c r="K24" t="n">
-        <v>1268</v>
+        <v>993</v>
       </c>
       <c r="L24" t="n">
-        <v>1100.4</v>
+        <v>1117.4</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1128</v>
+        <v>1183</v>
       </c>
       <c r="C25" t="n">
-        <v>1030</v>
+        <v>1170</v>
       </c>
       <c r="D25" t="n">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E25" t="n">
-        <v>978</v>
+        <v>1121</v>
       </c>
       <c r="F25" t="n">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="G25" t="n">
-        <v>1033</v>
+        <v>1053</v>
       </c>
       <c r="H25" t="n">
-        <v>1024</v>
+        <v>1214</v>
       </c>
       <c r="I25" t="n">
-        <v>1124</v>
+        <v>1114</v>
       </c>
       <c r="J25" t="n">
-        <v>999</v>
+        <v>1282</v>
       </c>
       <c r="K25" t="n">
-        <v>1106</v>
+        <v>1259</v>
       </c>
       <c r="L25" t="n">
-        <v>1066</v>
+        <v>1160.4</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1139</v>
+        <v>1158</v>
       </c>
       <c r="C26" t="n">
-        <v>1185</v>
+        <v>952</v>
       </c>
       <c r="D26" t="n">
-        <v>1021</v>
+        <v>1098</v>
       </c>
       <c r="E26" t="n">
-        <v>1070</v>
+        <v>1054</v>
       </c>
       <c r="F26" t="n">
-        <v>1093</v>
+        <v>999</v>
       </c>
       <c r="G26" t="n">
-        <v>1118</v>
+        <v>981</v>
       </c>
       <c r="H26" t="n">
-        <v>1156</v>
+        <v>1091</v>
       </c>
       <c r="I26" t="n">
-        <v>1024</v>
+        <v>1083</v>
       </c>
       <c r="J26" t="n">
-        <v>979</v>
+        <v>1082</v>
       </c>
       <c r="K26" t="n">
-        <v>1044</v>
+        <v>1138</v>
       </c>
       <c r="L26" t="n">
-        <v>1082.9</v>
+        <v>1063.6</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="C27" t="n">
-        <v>1049</v>
+        <v>1087</v>
       </c>
       <c r="D27" t="n">
-        <v>1118</v>
+        <v>1230</v>
       </c>
       <c r="E27" t="n">
-        <v>1022</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="n">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="G27" t="n">
-        <v>1249</v>
+        <v>1157</v>
       </c>
       <c r="H27" t="n">
-        <v>1154</v>
+        <v>1085</v>
       </c>
       <c r="I27" t="n">
-        <v>1328</v>
+        <v>998</v>
       </c>
       <c r="J27" t="n">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="K27" t="n">
-        <v>1213</v>
+        <v>1135</v>
       </c>
       <c r="L27" t="n">
-        <v>1142.2</v>
+        <v>1133.4</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="C28" t="n">
-        <v>1025</v>
+        <v>1041</v>
       </c>
       <c r="D28" t="n">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="E28" t="n">
-        <v>1027</v>
+        <v>1071</v>
       </c>
       <c r="F28" t="n">
-        <v>990</v>
+        <v>1031</v>
       </c>
       <c r="G28" t="n">
-        <v>1216</v>
+        <v>943</v>
       </c>
       <c r="H28" t="n">
-        <v>1274</v>
+        <v>1060</v>
       </c>
       <c r="I28" t="n">
-        <v>1021</v>
+        <v>1090</v>
       </c>
       <c r="J28" t="n">
-        <v>1091</v>
+        <v>1028</v>
       </c>
       <c r="K28" t="n">
-        <v>1092</v>
+        <v>1048</v>
       </c>
       <c r="L28" t="n">
-        <v>1093.5</v>
+        <v>1049.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>929</v>
+        <v>1016</v>
       </c>
       <c r="C29" t="n">
-        <v>1046</v>
+        <v>1031</v>
       </c>
       <c r="D29" t="n">
-        <v>923</v>
+        <v>1128</v>
       </c>
       <c r="E29" t="n">
-        <v>1251</v>
+        <v>1100</v>
       </c>
       <c r="F29" t="n">
-        <v>928</v>
+        <v>1034</v>
       </c>
       <c r="G29" t="n">
-        <v>1220</v>
+        <v>1067</v>
       </c>
       <c r="H29" t="n">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="I29" t="n">
-        <v>1135</v>
+        <v>973</v>
       </c>
       <c r="J29" t="n">
-        <v>1107</v>
+        <v>1030</v>
       </c>
       <c r="K29" t="n">
-        <v>937</v>
+        <v>1023</v>
       </c>
       <c r="L29" t="n">
-        <v>1046</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1026</v>
+        <v>916</v>
       </c>
       <c r="C30" t="n">
-        <v>979</v>
+        <v>1011</v>
       </c>
       <c r="D30" t="n">
-        <v>911</v>
+        <v>1029</v>
       </c>
       <c r="E30" t="n">
-        <v>1195</v>
+        <v>872</v>
       </c>
       <c r="F30" t="n">
-        <v>1079</v>
+        <v>1059</v>
       </c>
       <c r="G30" t="n">
-        <v>994</v>
+        <v>1238</v>
       </c>
       <c r="H30" t="n">
-        <v>1093</v>
+        <v>1135</v>
       </c>
       <c r="I30" t="n">
-        <v>915</v>
+        <v>978</v>
       </c>
       <c r="J30" t="n">
-        <v>1133</v>
+        <v>999</v>
       </c>
       <c r="K30" t="n">
-        <v>1151</v>
+        <v>1134</v>
       </c>
       <c r="L30" t="n">
-        <v>1047.6</v>
+        <v>1037.1</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1097</v>
+        <v>1235</v>
       </c>
       <c r="C31" t="n">
-        <v>1204</v>
+        <v>1031</v>
       </c>
       <c r="D31" t="n">
-        <v>1239</v>
+        <v>1166</v>
       </c>
       <c r="E31" t="n">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F31" t="n">
-        <v>1198</v>
+        <v>1161</v>
       </c>
       <c r="G31" t="n">
-        <v>1190</v>
+        <v>1181</v>
       </c>
       <c r="H31" t="n">
-        <v>1047</v>
+        <v>1026</v>
       </c>
       <c r="I31" t="n">
-        <v>1093</v>
+        <v>1212</v>
       </c>
       <c r="J31" t="n">
-        <v>1076</v>
+        <v>1251</v>
       </c>
       <c r="K31" t="n">
-        <v>1311</v>
+        <v>1105</v>
       </c>
       <c r="L31" t="n">
-        <v>1151.5</v>
+        <v>1142.9</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>887</v>
+        <v>1039</v>
       </c>
       <c r="C32" t="n">
-        <v>948</v>
+        <v>923</v>
       </c>
       <c r="D32" t="n">
-        <v>1091</v>
+        <v>939</v>
       </c>
       <c r="E32" t="n">
-        <v>1010</v>
+        <v>949</v>
       </c>
       <c r="F32" t="n">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="G32" t="n">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="H32" t="n">
-        <v>1312</v>
+        <v>978</v>
       </c>
       <c r="I32" t="n">
-        <v>997</v>
+        <v>864</v>
       </c>
       <c r="J32" t="n">
-        <v>1128</v>
+        <v>945</v>
       </c>
       <c r="K32" t="n">
-        <v>1173</v>
+        <v>922</v>
       </c>
       <c r="L32" t="n">
-        <v>1054.1</v>
+        <v>954.7</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1063</v>
+        <v>1155</v>
       </c>
       <c r="C33" t="n">
-        <v>1045</v>
+        <v>1010</v>
       </c>
       <c r="D33" t="n">
-        <v>1378</v>
+        <v>965</v>
       </c>
       <c r="E33" t="n">
-        <v>1117</v>
+        <v>1000</v>
       </c>
       <c r="F33" t="n">
-        <v>1016</v>
+        <v>1175</v>
       </c>
       <c r="G33" t="n">
-        <v>1111</v>
+        <v>1020</v>
       </c>
       <c r="H33" t="n">
-        <v>960</v>
+        <v>1019</v>
       </c>
       <c r="I33" t="n">
-        <v>1070</v>
+        <v>1193</v>
       </c>
       <c r="J33" t="n">
-        <v>1072</v>
+        <v>1030</v>
       </c>
       <c r="K33" t="n">
-        <v>990</v>
+        <v>1031</v>
       </c>
       <c r="L33" t="n">
-        <v>1082.2</v>
+        <v>1059.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="C34" t="n">
-        <v>1038</v>
+        <v>1174</v>
       </c>
       <c r="D34" t="n">
-        <v>1074</v>
+        <v>1003</v>
       </c>
       <c r="E34" t="n">
-        <v>973</v>
+        <v>1070</v>
       </c>
       <c r="F34" t="n">
-        <v>1041</v>
+        <v>1181</v>
       </c>
       <c r="G34" t="n">
-        <v>1134</v>
+        <v>1102</v>
       </c>
       <c r="H34" t="n">
-        <v>1259</v>
+        <v>1094</v>
       </c>
       <c r="I34" t="n">
-        <v>1236</v>
+        <v>1069</v>
       </c>
       <c r="J34" t="n">
-        <v>1079</v>
+        <v>1143</v>
       </c>
       <c r="K34" t="n">
-        <v>1104</v>
+        <v>1146</v>
       </c>
       <c r="L34" t="n">
-        <v>1099.8</v>
+        <v>1108.2</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1057</v>
+        <v>1195</v>
       </c>
       <c r="C35" t="n">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D35" t="n">
-        <v>1094</v>
+        <v>1063</v>
       </c>
       <c r="E35" t="n">
-        <v>1022</v>
+        <v>1055</v>
       </c>
       <c r="F35" t="n">
-        <v>1343</v>
+        <v>1217</v>
       </c>
       <c r="G35" t="n">
-        <v>1083</v>
+        <v>989</v>
       </c>
       <c r="H35" t="n">
-        <v>1041</v>
+        <v>984</v>
       </c>
       <c r="I35" t="n">
-        <v>1060</v>
+        <v>1038</v>
       </c>
       <c r="J35" t="n">
-        <v>1201</v>
+        <v>1033</v>
       </c>
       <c r="K35" t="n">
-        <v>1086</v>
+        <v>968</v>
       </c>
       <c r="L35" t="n">
-        <v>1104.6</v>
+        <v>1059.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
+        <v>1142</v>
+      </c>
+      <c r="C36" t="n">
         <v>1001</v>
       </c>
-      <c r="C36" t="n">
-        <v>1194</v>
-      </c>
       <c r="D36" t="n">
-        <v>1039</v>
+        <v>1105</v>
       </c>
       <c r="E36" t="n">
-        <v>1216</v>
+        <v>1143</v>
       </c>
       <c r="F36" t="n">
-        <v>873</v>
+        <v>1020</v>
       </c>
       <c r="G36" t="n">
-        <v>1123</v>
+        <v>952</v>
       </c>
       <c r="H36" t="n">
-        <v>1107</v>
+        <v>1088</v>
       </c>
       <c r="I36" t="n">
-        <v>985</v>
+        <v>1105</v>
       </c>
       <c r="J36" t="n">
-        <v>1260</v>
+        <v>1125</v>
       </c>
       <c r="K36" t="n">
-        <v>1032</v>
+        <v>1102</v>
       </c>
       <c r="L36" t="n">
-        <v>1083</v>
+        <v>1078.3</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>975</v>
+        <v>1042</v>
       </c>
       <c r="C37" t="n">
-        <v>1111</v>
+        <v>961</v>
       </c>
       <c r="D37" t="n">
-        <v>972</v>
+        <v>1103</v>
       </c>
       <c r="E37" t="n">
-        <v>1019</v>
+        <v>1114</v>
       </c>
       <c r="F37" t="n">
-        <v>1061</v>
+        <v>971</v>
       </c>
       <c r="G37" t="n">
-        <v>1084</v>
+        <v>1101</v>
       </c>
       <c r="H37" t="n">
-        <v>1116</v>
+        <v>1069</v>
       </c>
       <c r="I37" t="n">
-        <v>1114</v>
+        <v>1069</v>
       </c>
       <c r="J37" t="n">
-        <v>1074</v>
+        <v>1091</v>
       </c>
       <c r="K37" t="n">
-        <v>1157</v>
+        <v>1033</v>
       </c>
       <c r="L37" t="n">
-        <v>1068.3</v>
+        <v>1055.4</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1084</v>
+        <v>1125</v>
       </c>
       <c r="C38" t="n">
-        <v>1107</v>
+        <v>881</v>
       </c>
       <c r="D38" t="n">
-        <v>983</v>
+        <v>1155</v>
       </c>
       <c r="E38" t="n">
-        <v>1183</v>
+        <v>945</v>
       </c>
       <c r="F38" t="n">
-        <v>962</v>
+        <v>998</v>
       </c>
       <c r="G38" t="n">
-        <v>992</v>
+        <v>1016</v>
       </c>
       <c r="H38" t="n">
-        <v>1185</v>
+        <v>1201</v>
       </c>
       <c r="I38" t="n">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="J38" t="n">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="K38" t="n">
-        <v>1017</v>
+        <v>946</v>
       </c>
       <c r="L38" t="n">
-        <v>1054.3</v>
+        <v>1026.7</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>975</v>
+        <v>949</v>
       </c>
       <c r="C39" t="n">
-        <v>1111</v>
+        <v>1022</v>
       </c>
       <c r="D39" t="n">
-        <v>933</v>
+        <v>1016</v>
       </c>
       <c r="E39" t="n">
-        <v>1145</v>
+        <v>1010</v>
       </c>
       <c r="F39" t="n">
-        <v>1075</v>
+        <v>1022</v>
       </c>
       <c r="G39" t="n">
-        <v>977</v>
+        <v>956</v>
       </c>
       <c r="H39" t="n">
-        <v>960</v>
+        <v>1084</v>
       </c>
       <c r="I39" t="n">
-        <v>1128</v>
+        <v>1024</v>
       </c>
       <c r="J39" t="n">
-        <v>1043</v>
+        <v>1188</v>
       </c>
       <c r="K39" t="n">
-        <v>1229</v>
+        <v>1047</v>
       </c>
       <c r="L39" t="n">
-        <v>1057.6</v>
+        <v>1031.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1121</v>
+        <v>1023</v>
       </c>
       <c r="C40" t="n">
-        <v>1022</v>
+        <v>939</v>
       </c>
       <c r="D40" t="n">
-        <v>1222</v>
+        <v>1030</v>
       </c>
       <c r="E40" t="n">
-        <v>1055</v>
+        <v>1142</v>
       </c>
       <c r="F40" t="n">
-        <v>1144</v>
+        <v>1024</v>
       </c>
       <c r="G40" t="n">
-        <v>1070</v>
+        <v>1129</v>
       </c>
       <c r="H40" t="n">
-        <v>1019</v>
+        <v>1192</v>
       </c>
       <c r="I40" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="J40" t="n">
-        <v>1202</v>
+        <v>996</v>
       </c>
       <c r="K40" t="n">
-        <v>1030</v>
+        <v>1138</v>
       </c>
       <c r="L40" t="n">
-        <v>1105</v>
+        <v>1077.9</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1110</v>
+        <v>1072</v>
       </c>
       <c r="C41" t="n">
-        <v>909</v>
+        <v>1217</v>
       </c>
       <c r="D41" t="n">
-        <v>1064</v>
+        <v>1016</v>
       </c>
       <c r="E41" t="n">
-        <v>1130</v>
+        <v>1054</v>
       </c>
       <c r="F41" t="n">
-        <v>1118</v>
+        <v>1054</v>
       </c>
       <c r="G41" t="n">
-        <v>1253</v>
+        <v>1166</v>
       </c>
       <c r="H41" t="n">
-        <v>1034</v>
+        <v>999</v>
       </c>
       <c r="I41" t="n">
-        <v>889</v>
+        <v>1063</v>
       </c>
       <c r="J41" t="n">
-        <v>936</v>
+        <v>1003</v>
       </c>
       <c r="K41" t="n">
-        <v>932</v>
+        <v>1215</v>
       </c>
       <c r="L41" t="n">
-        <v>1037.5</v>
+        <v>1085.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C42" t="n">
-        <v>1070</v>
+        <v>989</v>
       </c>
       <c r="D42" t="n">
-        <v>1043</v>
+        <v>991</v>
       </c>
       <c r="E42" t="n">
-        <v>997</v>
+        <v>1125</v>
       </c>
       <c r="F42" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G42" t="n">
-        <v>1065</v>
+        <v>1147</v>
       </c>
       <c r="H42" t="n">
-        <v>1019</v>
+        <v>1035</v>
       </c>
       <c r="I42" t="n">
-        <v>987</v>
+        <v>1225</v>
       </c>
       <c r="J42" t="n">
-        <v>1072</v>
+        <v>1106</v>
       </c>
       <c r="K42" t="n">
-        <v>883</v>
+        <v>1095</v>
       </c>
       <c r="L42" t="n">
-        <v>1021.2</v>
+        <v>1078.9</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1221</v>
+        <v>1099</v>
       </c>
       <c r="C43" t="n">
-        <v>1019</v>
+        <v>1135</v>
       </c>
       <c r="D43" t="n">
-        <v>1178</v>
+        <v>1280</v>
       </c>
       <c r="E43" t="n">
-        <v>1099</v>
+        <v>1057</v>
       </c>
       <c r="F43" t="n">
-        <v>1210</v>
+        <v>1111</v>
       </c>
       <c r="G43" t="n">
-        <v>1301</v>
+        <v>1175</v>
       </c>
       <c r="H43" t="n">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="I43" t="n">
-        <v>1059</v>
+        <v>1083</v>
       </c>
       <c r="J43" t="n">
-        <v>1198</v>
+        <v>1352</v>
       </c>
       <c r="K43" t="n">
-        <v>1156</v>
+        <v>985</v>
       </c>
       <c r="L43" t="n">
-        <v>1148.6</v>
+        <v>1133.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1054</v>
+        <v>1125</v>
       </c>
       <c r="C44" t="n">
-        <v>1205</v>
+        <v>1272</v>
       </c>
       <c r="D44" t="n">
-        <v>1185</v>
+        <v>1107</v>
       </c>
       <c r="E44" t="n">
-        <v>1122</v>
+        <v>1074</v>
       </c>
       <c r="F44" t="n">
-        <v>1241</v>
+        <v>1147</v>
       </c>
       <c r="G44" t="n">
-        <v>1215</v>
+        <v>1087</v>
       </c>
       <c r="H44" t="n">
-        <v>1027</v>
+        <v>983</v>
       </c>
       <c r="I44" t="n">
-        <v>1107</v>
+        <v>1230</v>
       </c>
       <c r="J44" t="n">
-        <v>1262</v>
+        <v>1043</v>
       </c>
       <c r="K44" t="n">
-        <v>1022</v>
+        <v>1228</v>
       </c>
       <c r="L44" t="n">
-        <v>1144</v>
+        <v>1129.6</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="C45" t="n">
-        <v>1111</v>
+        <v>1054</v>
       </c>
       <c r="D45" t="n">
-        <v>921</v>
+        <v>991</v>
       </c>
       <c r="E45" t="n">
-        <v>1035</v>
+        <v>1240</v>
       </c>
       <c r="F45" t="n">
-        <v>1241</v>
+        <v>1064</v>
       </c>
       <c r="G45" t="n">
-        <v>1090</v>
+        <v>947</v>
       </c>
       <c r="H45" t="n">
-        <v>1050</v>
+        <v>1024</v>
       </c>
       <c r="I45" t="n">
-        <v>1099</v>
+        <v>1375</v>
       </c>
       <c r="J45" t="n">
-        <v>1070</v>
+        <v>986</v>
       </c>
       <c r="K45" t="n">
-        <v>1106</v>
+        <v>1081</v>
       </c>
       <c r="L45" t="n">
-        <v>1072.7</v>
+        <v>1075.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1152</v>
+        <v>1133</v>
       </c>
       <c r="C46" t="n">
-        <v>1133</v>
+        <v>1091</v>
       </c>
       <c r="D46" t="n">
-        <v>1152</v>
+        <v>1214</v>
       </c>
       <c r="E46" t="n">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="F46" t="n">
-        <v>1195</v>
+        <v>1072</v>
       </c>
       <c r="G46" t="n">
+        <v>1216</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1231</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1089</v>
+      </c>
+      <c r="J46" t="n">
         <v>1310</v>
       </c>
-      <c r="H46" t="n">
-        <v>1178</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1038</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1166</v>
-      </c>
       <c r="K46" t="n">
-        <v>964</v>
+        <v>1146</v>
       </c>
       <c r="L46" t="n">
-        <v>1144.1</v>
+        <v>1164.9</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1131</v>
+        <v>1107</v>
       </c>
       <c r="C47" t="n">
-        <v>1163</v>
+        <v>1075</v>
       </c>
       <c r="D47" t="n">
-        <v>1121</v>
+        <v>1186</v>
       </c>
       <c r="E47" t="n">
-        <v>1099</v>
+        <v>1052</v>
       </c>
       <c r="F47" t="n">
-        <v>1097</v>
+        <v>1208</v>
       </c>
       <c r="G47" t="n">
-        <v>1003</v>
+        <v>1067</v>
       </c>
       <c r="H47" t="n">
-        <v>1116</v>
+        <v>1182</v>
       </c>
       <c r="I47" t="n">
-        <v>1181</v>
+        <v>1275</v>
       </c>
       <c r="J47" t="n">
-        <v>1128</v>
+        <v>1204</v>
       </c>
       <c r="K47" t="n">
-        <v>1151</v>
+        <v>1040</v>
       </c>
       <c r="L47" t="n">
-        <v>1119</v>
+        <v>1139.6</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1130</v>
+        <v>977</v>
       </c>
       <c r="C48" t="n">
-        <v>1127</v>
+        <v>1108</v>
       </c>
       <c r="D48" t="n">
-        <v>1118</v>
+        <v>1050</v>
       </c>
       <c r="E48" t="n">
-        <v>1189</v>
+        <v>1024</v>
       </c>
       <c r="F48" t="n">
-        <v>1062</v>
+        <v>1083</v>
       </c>
       <c r="G48" t="n">
-        <v>1078</v>
+        <v>1205</v>
       </c>
       <c r="H48" t="n">
-        <v>1157</v>
+        <v>1037</v>
       </c>
       <c r="I48" t="n">
-        <v>1184</v>
+        <v>1107</v>
       </c>
       <c r="J48" t="n">
-        <v>1238</v>
+        <v>1030</v>
       </c>
       <c r="K48" t="n">
-        <v>1050</v>
+        <v>1247</v>
       </c>
       <c r="L48" t="n">
-        <v>1133.3</v>
+        <v>1086.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,28 +2257,28 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>980</v>
+        <v>1015</v>
       </c>
       <c r="C49" t="n">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D49" t="n">
-        <v>1209</v>
+        <v>1104</v>
       </c>
       <c r="E49" t="n">
-        <v>1048</v>
+        <v>1130</v>
       </c>
       <c r="F49" t="n">
-        <v>1058</v>
+        <v>1083</v>
       </c>
       <c r="G49" t="n">
-        <v>1109</v>
+        <v>1086</v>
       </c>
       <c r="H49" t="n">
-        <v>1028</v>
+        <v>1271</v>
       </c>
       <c r="I49" t="n">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="J49" t="n">
         <v>1040</v>
@@ -2287,7 +2287,7 @@
         <v>1076</v>
       </c>
       <c r="L49" t="n">
-        <v>1084.7</v>
+        <v>1111.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1090</v>
+        <v>1013</v>
       </c>
       <c r="C50" t="n">
-        <v>996</v>
+        <v>1220</v>
       </c>
       <c r="D50" t="n">
-        <v>1043</v>
+        <v>1084</v>
       </c>
       <c r="E50" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F50" t="n">
-        <v>894</v>
+        <v>948</v>
       </c>
       <c r="G50" t="n">
-        <v>950</v>
+        <v>982</v>
       </c>
       <c r="H50" t="n">
-        <v>829</v>
+        <v>1015</v>
       </c>
       <c r="I50" t="n">
-        <v>996</v>
+        <v>1165</v>
       </c>
       <c r="J50" t="n">
-        <v>1113</v>
+        <v>946</v>
       </c>
       <c r="K50" t="n">
-        <v>1079</v>
+        <v>849</v>
       </c>
       <c r="L50" t="n">
-        <v>996.2</v>
+        <v>1019.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1096</v>
+        <v>1080</v>
       </c>
       <c r="C51" t="n">
-        <v>990</v>
+        <v>963</v>
       </c>
       <c r="D51" t="n">
-        <v>990</v>
+        <v>1134</v>
       </c>
       <c r="E51" t="n">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="F51" t="n">
-        <v>947</v>
+        <v>1015</v>
       </c>
       <c r="G51" t="n">
-        <v>1171</v>
+        <v>1186</v>
       </c>
       <c r="H51" t="n">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="I51" t="n">
-        <v>935</v>
+        <v>1011</v>
       </c>
       <c r="J51" t="n">
-        <v>1088</v>
+        <v>1208</v>
       </c>
       <c r="K51" t="n">
-        <v>1102</v>
+        <v>1082</v>
       </c>
       <c r="L51" t="n">
-        <v>1037.1</v>
+        <v>1071.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1082.72</v>
+        <v>1081.04</v>
       </c>
       <c r="C52" t="n">
-        <v>1085.42</v>
+        <v>1078.58</v>
       </c>
       <c r="D52" t="n">
-        <v>1084.68</v>
+        <v>1093.06</v>
       </c>
       <c r="E52" t="n">
-        <v>1091.3</v>
+        <v>1091.46</v>
       </c>
       <c r="F52" t="n">
-        <v>1097.06</v>
+        <v>1074.7</v>
       </c>
       <c r="G52" t="n">
-        <v>1101.02</v>
+        <v>1087.2</v>
       </c>
       <c r="H52" t="n">
-        <v>1091.34</v>
+        <v>1092.06</v>
       </c>
       <c r="I52" t="n">
-        <v>1073.88</v>
+        <v>1106.46</v>
       </c>
       <c r="J52" t="n">
-        <v>1110.04</v>
+        <v>1096.76</v>
       </c>
       <c r="K52" t="n">
-        <v>1095</v>
+        <v>1096.66</v>
       </c>
       <c r="L52" t="n">
-        <v>1091.246</v>
+        <v>1089.798</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>13.30967593193054</v>
+        <v>11.75356793403625</v>
       </c>
       <c r="C2" t="n">
-        <v>13.65822720527649</v>
+        <v>13.79943656921387</v>
       </c>
       <c r="D2" t="n">
-        <v>11.56709837913513</v>
+        <v>11.98150539398193</v>
       </c>
       <c r="E2" t="n">
-        <v>11.07929396629333</v>
+        <v>11.20248532295227</v>
       </c>
       <c r="F2" t="n">
-        <v>12.68173217773438</v>
+        <v>11.80897521972656</v>
       </c>
       <c r="G2" t="n">
-        <v>10.98503184318542</v>
+        <v>14.23076367378235</v>
       </c>
       <c r="H2" t="n">
-        <v>12.0264036655426</v>
+        <v>12.42934894561768</v>
       </c>
       <c r="I2" t="n">
-        <v>12.42938089370728</v>
+        <v>11.96002793312073</v>
       </c>
       <c r="J2" t="n">
-        <v>11.91357183456421</v>
+        <v>10.96560478210449</v>
       </c>
       <c r="K2" t="n">
-        <v>11.39246344566345</v>
+        <v>12.30317378044128</v>
       </c>
       <c r="L2" t="n">
-        <v>12.10428793430328</v>
+        <v>12.24348895549774</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>10.38008427619934</v>
+        <v>11.13413858413696</v>
       </c>
       <c r="C3" t="n">
-        <v>10.84041047096252</v>
+        <v>10.19900631904602</v>
       </c>
       <c r="D3" t="n">
-        <v>11.99743270874023</v>
+        <v>14.4123215675354</v>
       </c>
       <c r="E3" t="n">
-        <v>15.87952470779419</v>
+        <v>12.19044184684753</v>
       </c>
       <c r="F3" t="n">
-        <v>11.62535643577576</v>
+        <v>11.10525846481323</v>
       </c>
       <c r="G3" t="n">
-        <v>11.18253517150879</v>
+        <v>10.7182765007019</v>
       </c>
       <c r="H3" t="n">
-        <v>14.92847776412964</v>
+        <v>10.60645627975464</v>
       </c>
       <c r="I3" t="n">
-        <v>10.09979104995728</v>
+        <v>11.44423246383667</v>
       </c>
       <c r="J3" t="n">
-        <v>12.12018322944641</v>
+        <v>9.918670415878296</v>
       </c>
       <c r="K3" t="n">
-        <v>10.69522881507874</v>
+        <v>13.45605230331421</v>
       </c>
       <c r="L3" t="n">
-        <v>11.97490246295929</v>
+        <v>11.51848547458649</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>14.5105574131012</v>
+        <v>12.5578875541687</v>
       </c>
       <c r="C4" t="n">
-        <v>14.0156044960022</v>
+        <v>12.18480920791626</v>
       </c>
       <c r="D4" t="n">
-        <v>11.12416338920593</v>
+        <v>12.00395727157593</v>
       </c>
       <c r="E4" t="n">
-        <v>15.51502370834351</v>
+        <v>12.64974427223206</v>
       </c>
       <c r="F4" t="n">
-        <v>11.88375210762024</v>
+        <v>11.61840772628784</v>
       </c>
       <c r="G4" t="n">
-        <v>11.70470547676086</v>
+        <v>11.76356053352356</v>
       </c>
       <c r="H4" t="n">
-        <v>11.95903134346008</v>
+        <v>11.6688027381897</v>
       </c>
       <c r="I4" t="n">
-        <v>16.31597900390625</v>
+        <v>13.44076490402222</v>
       </c>
       <c r="J4" t="n">
-        <v>17.56079602241516</v>
+        <v>11.97609639167786</v>
       </c>
       <c r="K4" t="n">
-        <v>12.55351233482361</v>
+        <v>11.63639068603516</v>
       </c>
       <c r="L4" t="n">
-        <v>13.7143125295639</v>
+        <v>12.15004212856293</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>11.19903683662415</v>
+        <v>9.840943574905396</v>
       </c>
       <c r="C5" t="n">
-        <v>10.41846346855164</v>
+        <v>10.6528742313385</v>
       </c>
       <c r="D5" t="n">
-        <v>10.66037893295288</v>
+        <v>10.48778653144836</v>
       </c>
       <c r="E5" t="n">
-        <v>9.496890306472778</v>
+        <v>9.679326772689819</v>
       </c>
       <c r="F5" t="n">
-        <v>11.0153214931488</v>
+        <v>12.97891473770142</v>
       </c>
       <c r="G5" t="n">
-        <v>10.35283732414246</v>
+        <v>10.23721790313721</v>
       </c>
       <c r="H5" t="n">
-        <v>10.34969782829285</v>
+        <v>11.15352892875671</v>
       </c>
       <c r="I5" t="n">
-        <v>10.29475545883179</v>
+        <v>10.95055294036865</v>
       </c>
       <c r="J5" t="n">
-        <v>10.19205951690674</v>
+        <v>10.90649938583374</v>
       </c>
       <c r="K5" t="n">
-        <v>12.17101073265076</v>
+        <v>10.99699234962463</v>
       </c>
       <c r="L5" t="n">
-        <v>10.61504518985748</v>
+        <v>10.78846373558044</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>13.35446095466614</v>
+        <v>10.95363330841064</v>
       </c>
       <c r="C6" t="n">
-        <v>11.83790445327759</v>
+        <v>10.93916392326355</v>
       </c>
       <c r="D6" t="n">
-        <v>11.09627938270569</v>
+        <v>11.33359241485596</v>
       </c>
       <c r="E6" t="n">
-        <v>13.48271751403809</v>
+        <v>11.39048767089844</v>
       </c>
       <c r="F6" t="n">
-        <v>11.52693438529968</v>
+        <v>11.4533326625824</v>
       </c>
       <c r="G6" t="n">
-        <v>11.18948721885681</v>
+        <v>12.56426215171814</v>
       </c>
       <c r="H6" t="n">
-        <v>12.96047472953796</v>
+        <v>10.98094177246094</v>
       </c>
       <c r="I6" t="n">
-        <v>10.40752410888672</v>
+        <v>11.10767531394958</v>
       </c>
       <c r="J6" t="n">
-        <v>10.82341933250427</v>
+        <v>10.43184924125671</v>
       </c>
       <c r="K6" t="n">
-        <v>10.91571426391602</v>
+        <v>14.47684240341187</v>
       </c>
       <c r="L6" t="n">
-        <v>11.7594916343689</v>
+        <v>11.56317808628082</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>11.10571551322937</v>
+        <v>11.65271544456482</v>
       </c>
       <c r="C7" t="n">
-        <v>11.74263858795166</v>
+        <v>10.83385157585144</v>
       </c>
       <c r="D7" t="n">
-        <v>10.74964618682861</v>
+        <v>11.77238869667053</v>
       </c>
       <c r="E7" t="n">
-        <v>10.93565225601196</v>
+        <v>13.34082889556885</v>
       </c>
       <c r="F7" t="n">
-        <v>13.22918391227722</v>
+        <v>10.99690222740173</v>
       </c>
       <c r="G7" t="n">
-        <v>11.03204131126404</v>
+        <v>13.80608320236206</v>
       </c>
       <c r="H7" t="n">
-        <v>11.25935935974121</v>
+        <v>10.78594851493835</v>
       </c>
       <c r="I7" t="n">
-        <v>10.83043718338013</v>
+        <v>14.10229110717773</v>
       </c>
       <c r="J7" t="n">
-        <v>12.01837420463562</v>
+        <v>14.19406247138977</v>
       </c>
       <c r="K7" t="n">
-        <v>11.67476654052734</v>
+        <v>11.14805865287781</v>
       </c>
       <c r="L7" t="n">
-        <v>11.45778150558472</v>
+        <v>12.26331307888031</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68669652938843</v>
+        <v>11.60893678665161</v>
       </c>
       <c r="C8" t="n">
-        <v>11.42790818214417</v>
+        <v>12.38653326034546</v>
       </c>
       <c r="D8" t="n">
-        <v>11.40796279907227</v>
+        <v>13.76048493385315</v>
       </c>
       <c r="E8" t="n">
-        <v>11.3380401134491</v>
+        <v>12.76250052452087</v>
       </c>
       <c r="F8" t="n">
-        <v>11.3955602645874</v>
+        <v>10.23990941047668</v>
       </c>
       <c r="G8" t="n">
-        <v>11.36557936668396</v>
+        <v>11.28928828239441</v>
       </c>
       <c r="H8" t="n">
-        <v>11.53610825538635</v>
+        <v>12.93357515335083</v>
       </c>
       <c r="I8" t="n">
-        <v>10.8997323513031</v>
+        <v>10.36063170433044</v>
       </c>
       <c r="J8" t="n">
-        <v>11.9590380191803</v>
+        <v>15.47954964637756</v>
       </c>
       <c r="K8" t="n">
-        <v>12.64580059051514</v>
+        <v>16.09249973297119</v>
       </c>
       <c r="L8" t="n">
-        <v>11.66624264717102</v>
+        <v>12.69139094352722</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>10.90224456787109</v>
+        <v>11.36158084869385</v>
       </c>
       <c r="C9" t="n">
-        <v>10.344731092453</v>
+        <v>11.21345472335815</v>
       </c>
       <c r="D9" t="n">
-        <v>10.59251666069031</v>
+        <v>10.78354525566101</v>
       </c>
       <c r="E9" t="n">
-        <v>10.84143352508545</v>
+        <v>11.04784250259399</v>
       </c>
       <c r="F9" t="n">
-        <v>11.46232461929321</v>
+        <v>11.06777548789978</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9340193271637</v>
+        <v>11.30871748924255</v>
       </c>
       <c r="H9" t="n">
-        <v>13.03380537033081</v>
+        <v>10.25391507148743</v>
       </c>
       <c r="I9" t="n">
-        <v>12.10276699066162</v>
+        <v>10.9880096912384</v>
       </c>
       <c r="J9" t="n">
-        <v>11.886878490448</v>
+        <v>15.64588451385498</v>
       </c>
       <c r="K9" t="n">
-        <v>12.34211587905884</v>
+        <v>11.03188943862915</v>
       </c>
       <c r="L9" t="n">
-        <v>11.7442836523056</v>
+        <v>11.47026150226593</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>10.97106528282166</v>
+        <v>12.45578122138977</v>
       </c>
       <c r="C10" t="n">
-        <v>11.69321155548096</v>
+        <v>13.82172393798828</v>
       </c>
       <c r="D10" t="n">
-        <v>13.39992928504944</v>
+        <v>12.53738045692444</v>
       </c>
       <c r="E10" t="n">
-        <v>12.05725383758545</v>
+        <v>11.02990818023682</v>
       </c>
       <c r="F10" t="n">
-        <v>15.72545075416565</v>
+        <v>10.72716736793518</v>
       </c>
       <c r="G10" t="n">
-        <v>10.47682666778564</v>
+        <v>11.37753057479858</v>
       </c>
       <c r="H10" t="n">
-        <v>11.77153921127319</v>
+        <v>10.47814512252808</v>
       </c>
       <c r="I10" t="n">
-        <v>11.66092848777771</v>
+        <v>10.57647752761841</v>
       </c>
       <c r="J10" t="n">
-        <v>11.6148898601532</v>
+        <v>11.76800894737244</v>
       </c>
       <c r="K10" t="n">
-        <v>15.78679728507996</v>
+        <v>11.19800662994385</v>
       </c>
       <c r="L10" t="n">
-        <v>12.51578922271728</v>
+        <v>11.59701299667358</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>12.14056420326233</v>
+        <v>16.77280592918396</v>
       </c>
       <c r="C11" t="n">
-        <v>11.85579490661621</v>
+        <v>11.02294087409973</v>
       </c>
       <c r="D11" t="n">
-        <v>11.69957447052002</v>
+        <v>11.87580537796021</v>
       </c>
       <c r="E11" t="n">
-        <v>14.93363285064697</v>
+        <v>16.55433678627014</v>
       </c>
       <c r="F11" t="n">
-        <v>10.82587361335754</v>
+        <v>11.46930742263794</v>
       </c>
       <c r="G11" t="n">
-        <v>10.93405747413635</v>
+        <v>11.35959410667419</v>
       </c>
       <c r="H11" t="n">
-        <v>11.32210731506348</v>
+        <v>16.46006488800049</v>
       </c>
       <c r="I11" t="n">
-        <v>11.97387838363647</v>
+        <v>11.51516246795654</v>
       </c>
       <c r="J11" t="n">
-        <v>10.50266075134277</v>
+        <v>11.34657764434814</v>
       </c>
       <c r="K11" t="n">
-        <v>11.96889019012451</v>
+        <v>11.26033735275269</v>
       </c>
       <c r="L11" t="n">
-        <v>11.81570341587067</v>
+        <v>12.9636932849884</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>15.84582090377808</v>
+        <v>14.42627215385437</v>
       </c>
       <c r="C12" t="n">
-        <v>14.83923435211182</v>
+        <v>15.29453921318054</v>
       </c>
       <c r="D12" t="n">
-        <v>12.26628255844116</v>
+        <v>11.87279748916626</v>
       </c>
       <c r="E12" t="n">
-        <v>12.80685138702393</v>
+        <v>14.04719948768616</v>
       </c>
       <c r="F12" t="n">
-        <v>13.21729731559753</v>
+        <v>12.03044056892395</v>
       </c>
       <c r="G12" t="n">
-        <v>13.58545708656311</v>
+        <v>13.5390088558197</v>
       </c>
       <c r="H12" t="n">
-        <v>11.32572770118713</v>
+        <v>12.3605272769928</v>
       </c>
       <c r="I12" t="n">
-        <v>11.08976626396179</v>
+        <v>11.19680619239807</v>
       </c>
       <c r="J12" t="n">
-        <v>12.13559174537659</v>
+        <v>15.27860593795776</v>
       </c>
       <c r="K12" t="n">
-        <v>11.41092276573181</v>
+        <v>12.12765288352966</v>
       </c>
       <c r="L12" t="n">
-        <v>12.8522952079773</v>
+        <v>13.21738500595093</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>11.92119574546814</v>
+        <v>12.15251207351685</v>
       </c>
       <c r="C13" t="n">
-        <v>11.62039756774902</v>
+        <v>12.29318022727966</v>
       </c>
       <c r="D13" t="n">
-        <v>12.78743577003479</v>
+        <v>12.27974557876587</v>
       </c>
       <c r="E13" t="n">
-        <v>11.80990362167358</v>
+        <v>14.56292319297791</v>
       </c>
       <c r="F13" t="n">
-        <v>14.52601599693298</v>
+        <v>11.88072633743286</v>
       </c>
       <c r="G13" t="n">
-        <v>14.51252794265747</v>
+        <v>14.53546357154846</v>
       </c>
       <c r="H13" t="n">
-        <v>17.86436772346497</v>
+        <v>12.14357995986938</v>
       </c>
       <c r="I13" t="n">
-        <v>16.24263310432434</v>
+        <v>18.19063472747803</v>
       </c>
       <c r="J13" t="n">
-        <v>11.99345922470093</v>
+        <v>12.88373279571533</v>
       </c>
       <c r="K13" t="n">
-        <v>14.43225145339966</v>
+        <v>17.30247974395752</v>
       </c>
       <c r="L13" t="n">
-        <v>13.77101881504059</v>
+        <v>13.82249782085419</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>12.43634510040283</v>
+        <v>12.38079881668091</v>
       </c>
       <c r="C14" t="n">
-        <v>12.38745307922363</v>
+        <v>11.6397168636322</v>
       </c>
       <c r="D14" t="n">
-        <v>16.32009673118591</v>
+        <v>12.0417103767395</v>
       </c>
       <c r="E14" t="n">
-        <v>12.09553909301758</v>
+        <v>15.6254518032074</v>
       </c>
       <c r="F14" t="n">
-        <v>11.91753101348877</v>
+        <v>14.37883901596069</v>
       </c>
       <c r="G14" t="n">
-        <v>11.92751383781433</v>
+        <v>11.05584836006165</v>
       </c>
       <c r="H14" t="n">
-        <v>11.97077488899231</v>
+        <v>14.38836598396301</v>
       </c>
       <c r="I14" t="n">
-        <v>12.93172979354858</v>
+        <v>14.9404296875</v>
       </c>
       <c r="J14" t="n">
-        <v>14.74002766609192</v>
+        <v>11.98348426818848</v>
       </c>
       <c r="K14" t="n">
-        <v>10.8483681678772</v>
+        <v>13.30911755561829</v>
       </c>
       <c r="L14" t="n">
-        <v>12.75753793716431</v>
+        <v>13.17437627315521</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>13.24822878837585</v>
+        <v>11.46180009841919</v>
       </c>
       <c r="C15" t="n">
-        <v>15.00878238677979</v>
+        <v>11.31872296333313</v>
       </c>
       <c r="D15" t="n">
-        <v>15.0605993270874</v>
+        <v>10.6838436126709</v>
       </c>
       <c r="E15" t="n">
-        <v>14.07096838951111</v>
+        <v>16.42632293701172</v>
       </c>
       <c r="F15" t="n">
-        <v>14.65802836418152</v>
+        <v>11.18292593955994</v>
       </c>
       <c r="G15" t="n">
-        <v>10.90416073799133</v>
+        <v>11.66467571258545</v>
       </c>
       <c r="H15" t="n">
-        <v>10.83681011199951</v>
+        <v>15.80186176300049</v>
       </c>
       <c r="I15" t="n">
-        <v>13.9121367931366</v>
+        <v>14.55545496940613</v>
       </c>
       <c r="J15" t="n">
-        <v>11.08870244026184</v>
+        <v>10.95158648490906</v>
       </c>
       <c r="K15" t="n">
-        <v>11.69910860061646</v>
+        <v>15.47710537910461</v>
       </c>
       <c r="L15" t="n">
-        <v>13.04875259399414</v>
+        <v>12.95242998600006</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>11.9234836101532</v>
+        <v>10.44842958450317</v>
       </c>
       <c r="C16" t="n">
-        <v>12.34738206863403</v>
+        <v>14.25368118286133</v>
       </c>
       <c r="D16" t="n">
-        <v>16.51255559921265</v>
+        <v>12.27930903434753</v>
       </c>
       <c r="E16" t="n">
-        <v>11.10213541984558</v>
+        <v>15.16283750534058</v>
       </c>
       <c r="F16" t="n">
-        <v>13.60062527656555</v>
+        <v>14.69812536239624</v>
       </c>
       <c r="G16" t="n">
-        <v>11.17397928237915</v>
+        <v>11.59753251075745</v>
       </c>
       <c r="H16" t="n">
-        <v>20.43669414520264</v>
+        <v>10.65588402748108</v>
       </c>
       <c r="I16" t="n">
-        <v>12.27567076683044</v>
+        <v>11.72071433067322</v>
       </c>
       <c r="J16" t="n">
-        <v>11.31507158279419</v>
+        <v>12.72107338905334</v>
       </c>
       <c r="K16" t="n">
-        <v>11.1714506149292</v>
+        <v>11.27726626396179</v>
       </c>
       <c r="L16" t="n">
-        <v>13.18590483665466</v>
+        <v>12.48148531913757</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>11.67512893676758</v>
+        <v>10.53368782997131</v>
       </c>
       <c r="C17" t="n">
-        <v>10.85183191299438</v>
+        <v>11.4713077545166</v>
       </c>
       <c r="D17" t="n">
-        <v>11.270179271698</v>
+        <v>12.29613924026489</v>
       </c>
       <c r="E17" t="n">
-        <v>11.05089926719666</v>
+        <v>13.05670380592346</v>
       </c>
       <c r="F17" t="n">
-        <v>11.17307567596436</v>
+        <v>11.39264321327209</v>
       </c>
       <c r="G17" t="n">
-        <v>11.36706233024597</v>
+        <v>11.53251123428345</v>
       </c>
       <c r="H17" t="n">
-        <v>10.9565749168396</v>
+        <v>11.2108519077301</v>
       </c>
       <c r="I17" t="n">
-        <v>11.59156894683838</v>
+        <v>10.09326410293579</v>
       </c>
       <c r="J17" t="n">
-        <v>10.8782947063446</v>
+        <v>11.28661227226257</v>
       </c>
       <c r="K17" t="n">
-        <v>15.2621169090271</v>
+        <v>14.19933843612671</v>
       </c>
       <c r="L17" t="n">
-        <v>11.60767328739166</v>
+        <v>11.7073059797287</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>13.55196523666382</v>
+        <v>15.45320892333984</v>
       </c>
       <c r="C18" t="n">
-        <v>15.11053514480591</v>
+        <v>15.26111459732056</v>
       </c>
       <c r="D18" t="n">
-        <v>11.60842370986938</v>
+        <v>11.4727623462677</v>
       </c>
       <c r="E18" t="n">
-        <v>11.93211436271667</v>
+        <v>13.00989389419556</v>
       </c>
       <c r="F18" t="n">
-        <v>12.71612811088562</v>
+        <v>13.32859325408936</v>
       </c>
       <c r="G18" t="n">
-        <v>14.57685160636902</v>
+        <v>17.21313762664795</v>
       </c>
       <c r="H18" t="n">
-        <v>14.99518203735352</v>
+        <v>10.98949527740479</v>
       </c>
       <c r="I18" t="n">
-        <v>14.48183369636536</v>
+        <v>11.16856074333191</v>
       </c>
       <c r="J18" t="n">
-        <v>13.15447616577148</v>
+        <v>10.89282035827637</v>
       </c>
       <c r="K18" t="n">
-        <v>14.22242045402527</v>
+        <v>12.05432081222534</v>
       </c>
       <c r="L18" t="n">
-        <v>13.6349930524826</v>
+        <v>13.08439078330994</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>11.08478569984436</v>
+        <v>11.26230573654175</v>
       </c>
       <c r="C19" t="n">
-        <v>11.39703321456909</v>
+        <v>11.36753582954407</v>
       </c>
       <c r="D19" t="n">
-        <v>10.72019386291504</v>
+        <v>16.12438797950745</v>
       </c>
       <c r="E19" t="n">
-        <v>10.46133875846863</v>
+        <v>11.32362771034241</v>
       </c>
       <c r="F19" t="n">
-        <v>13.75596213340759</v>
+        <v>11.159592628479</v>
       </c>
       <c r="G19" t="n">
-        <v>14.7260377407074</v>
+        <v>12.41384387016296</v>
       </c>
       <c r="H19" t="n">
-        <v>10.9536452293396</v>
+        <v>13.58137989044189</v>
       </c>
       <c r="I19" t="n">
-        <v>11.21247243881226</v>
+        <v>11.57897734642029</v>
       </c>
       <c r="J19" t="n">
-        <v>10.68877911567688</v>
+        <v>11.55056619644165</v>
       </c>
       <c r="K19" t="n">
-        <v>11.44384932518005</v>
+        <v>12.17092251777649</v>
       </c>
       <c r="L19" t="n">
-        <v>11.64440975189209</v>
+        <v>12.2533139705658</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>11.53609418869019</v>
+        <v>10.9202721118927</v>
       </c>
       <c r="C20" t="n">
-        <v>13.25561165809631</v>
+        <v>9.968069314956665</v>
       </c>
       <c r="D20" t="n">
-        <v>11.02133727073669</v>
+        <v>11.10789036750793</v>
       </c>
       <c r="E20" t="n">
-        <v>14.74612784385681</v>
+        <v>10.38147258758545</v>
       </c>
       <c r="F20" t="n">
-        <v>13.67777276039124</v>
+        <v>11.06633734703064</v>
       </c>
       <c r="G20" t="n">
-        <v>11.55660629272461</v>
+        <v>12.15204262733459</v>
       </c>
       <c r="H20" t="n">
-        <v>10.89228105545044</v>
+        <v>11.09971523284912</v>
       </c>
       <c r="I20" t="n">
-        <v>10.3192081451416</v>
+        <v>13.47321724891663</v>
       </c>
       <c r="J20" t="n">
-        <v>15.16838145256042</v>
+        <v>12.12060785293579</v>
       </c>
       <c r="K20" t="n">
-        <v>10.97156715393066</v>
+        <v>14.94548535346985</v>
       </c>
       <c r="L20" t="n">
-        <v>12.3144987821579</v>
+        <v>11.72351100444794</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>11.6054961681366</v>
+        <v>12.91875600814819</v>
       </c>
       <c r="C21" t="n">
-        <v>12.15354418754578</v>
+        <v>12.45435619354248</v>
       </c>
       <c r="D21" t="n">
-        <v>10.59006214141846</v>
+        <v>11.23038458824158</v>
       </c>
       <c r="E21" t="n">
-        <v>11.02692055702209</v>
+        <v>16.55269479751587</v>
       </c>
       <c r="F21" t="n">
-        <v>11.47300314903259</v>
+        <v>11.52728247642517</v>
       </c>
       <c r="G21" t="n">
-        <v>10.52510404586792</v>
+        <v>13.17245769500732</v>
       </c>
       <c r="H21" t="n">
-        <v>13.32384014129639</v>
+        <v>12.60437774658203</v>
       </c>
       <c r="I21" t="n">
-        <v>11.58983302116394</v>
+        <v>13.56696653366089</v>
       </c>
       <c r="J21" t="n">
-        <v>11.69232749938965</v>
+        <v>11.27345752716064</v>
       </c>
       <c r="K21" t="n">
-        <v>11.91861295700073</v>
+        <v>13.11840295791626</v>
       </c>
       <c r="L21" t="n">
-        <v>11.58987438678741</v>
+        <v>12.84191365242004</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>10.82641696929932</v>
+        <v>11.83123970031738</v>
       </c>
       <c r="C22" t="n">
-        <v>12.36149597167969</v>
+        <v>15.87924718856812</v>
       </c>
       <c r="D22" t="n">
-        <v>11.06324243545532</v>
+        <v>11.60383701324463</v>
       </c>
       <c r="E22" t="n">
-        <v>15.16507983207703</v>
+        <v>11.54849028587341</v>
       </c>
       <c r="F22" t="n">
-        <v>14.74219059944153</v>
+        <v>11.50960659980774</v>
       </c>
       <c r="G22" t="n">
-        <v>12.15641355514526</v>
+        <v>13.27344155311584</v>
       </c>
       <c r="H22" t="n">
-        <v>12.750319480896</v>
+        <v>10.84717798233032</v>
       </c>
       <c r="I22" t="n">
-        <v>10.34863686561584</v>
+        <v>11.76604819297791</v>
       </c>
       <c r="J22" t="n">
-        <v>14.74911856651306</v>
+        <v>12.19742059707642</v>
       </c>
       <c r="K22" t="n">
-        <v>11.9918372631073</v>
+        <v>12.11568164825439</v>
       </c>
       <c r="L22" t="n">
-        <v>12.61547515392303</v>
+        <v>12.25721907615662</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>10.93807005882263</v>
+        <v>10.47879195213318</v>
       </c>
       <c r="C23" t="n">
-        <v>10.44083499908447</v>
+        <v>13.07765555381775</v>
       </c>
       <c r="D23" t="n">
-        <v>10.3765230178833</v>
+        <v>10.91868495941162</v>
       </c>
       <c r="E23" t="n">
-        <v>13.56893062591553</v>
+        <v>10.60106492042542</v>
       </c>
       <c r="F23" t="n">
-        <v>10.72097873687744</v>
+        <v>10.13473653793335</v>
       </c>
       <c r="G23" t="n">
-        <v>10.52910590171814</v>
+        <v>11.0249183177948</v>
       </c>
       <c r="H23" t="n">
-        <v>10.71166086196899</v>
+        <v>10.65937662124634</v>
       </c>
       <c r="I23" t="n">
-        <v>10.26683616638184</v>
+        <v>11.57305407524109</v>
       </c>
       <c r="J23" t="n">
-        <v>13.37373518943787</v>
+        <v>11.9241099357605</v>
       </c>
       <c r="K23" t="n">
-        <v>11.78404188156128</v>
+        <v>14.60279607772827</v>
       </c>
       <c r="L23" t="n">
-        <v>11.27107174396515</v>
+        <v>11.49951889514923</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>11.46879148483276</v>
+        <v>12.2438747882843</v>
       </c>
       <c r="C24" t="n">
-        <v>12.02839493751526</v>
+        <v>14.54947352409363</v>
       </c>
       <c r="D24" t="n">
-        <v>11.16106009483337</v>
+        <v>11.54512524604797</v>
       </c>
       <c r="E24" t="n">
-        <v>12.03238439559937</v>
+        <v>12.16715264320374</v>
       </c>
       <c r="F24" t="n">
-        <v>11.71067380905151</v>
+        <v>12.33609461784363</v>
       </c>
       <c r="G24" t="n">
-        <v>11.47026300430298</v>
+        <v>10.84437561035156</v>
       </c>
       <c r="H24" t="n">
-        <v>12.03739905357361</v>
+        <v>14.71407270431519</v>
       </c>
       <c r="I24" t="n">
-        <v>15.50057029724121</v>
+        <v>12.11562180519104</v>
       </c>
       <c r="J24" t="n">
-        <v>13.44165015220642</v>
+        <v>11.39650678634644</v>
       </c>
       <c r="K24" t="n">
-        <v>15.08850789070129</v>
+        <v>11.06210517883301</v>
       </c>
       <c r="L24" t="n">
-        <v>12.59396951198578</v>
+        <v>12.29744029045105</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>15.42540526390076</v>
+        <v>12.90785789489746</v>
       </c>
       <c r="C25" t="n">
-        <v>12.52656769752502</v>
+        <v>13.57095837593079</v>
       </c>
       <c r="D25" t="n">
-        <v>13.30967259407043</v>
+        <v>13.05093050003052</v>
       </c>
       <c r="E25" t="n">
-        <v>12.2348301410675</v>
+        <v>13.7345232963562</v>
       </c>
       <c r="F25" t="n">
-        <v>12.78296184539795</v>
+        <v>12.64977478981018</v>
       </c>
       <c r="G25" t="n">
-        <v>13.84377408027649</v>
+        <v>12.65828967094421</v>
       </c>
       <c r="H25" t="n">
-        <v>11.7800133228302</v>
+        <v>14.78887724876404</v>
       </c>
       <c r="I25" t="n">
-        <v>12.74107813835144</v>
+        <v>15.34342360496521</v>
       </c>
       <c r="J25" t="n">
-        <v>12.32010650634766</v>
+        <v>16.39826273918152</v>
       </c>
       <c r="K25" t="n">
-        <v>13.45077109336853</v>
+        <v>17.21118831634521</v>
       </c>
       <c r="L25" t="n">
-        <v>13.0415180683136</v>
+        <v>14.23140864372253</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>13.09613847732544</v>
+        <v>11.21246004104614</v>
       </c>
       <c r="C26" t="n">
-        <v>14.17841601371765</v>
+        <v>9.859873294830322</v>
       </c>
       <c r="D26" t="n">
-        <v>9.820989608764648</v>
+        <v>10.6913104057312</v>
       </c>
       <c r="E26" t="n">
-        <v>11.48623847961426</v>
+        <v>9.819965839385986</v>
       </c>
       <c r="F26" t="n">
-        <v>12.22390270233154</v>
+        <v>10.13070631027222</v>
       </c>
       <c r="G26" t="n">
-        <v>11.26330184936523</v>
+        <v>9.446938991546631</v>
       </c>
       <c r="H26" t="n">
-        <v>13.57344150543213</v>
+        <v>11.0678493976593</v>
       </c>
       <c r="I26" t="n">
-        <v>9.908249855041504</v>
+        <v>10.40249228477478</v>
       </c>
       <c r="J26" t="n">
-        <v>9.69335150718689</v>
+        <v>10.58707094192505</v>
       </c>
       <c r="K26" t="n">
-        <v>10.2553985118866</v>
+        <v>10.71818614006042</v>
       </c>
       <c r="L26" t="n">
-        <v>11.54994285106659</v>
+        <v>10.39368536472321</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>11.40845608711243</v>
+        <v>11.18900799751282</v>
       </c>
       <c r="C27" t="n">
-        <v>11.65783715248108</v>
+        <v>10.93121290206909</v>
       </c>
       <c r="D27" t="n">
-        <v>13.72652173042297</v>
+        <v>14.66664218902588</v>
       </c>
       <c r="E27" t="n">
-        <v>11.65529561042786</v>
+        <v>14.53753066062927</v>
       </c>
       <c r="F27" t="n">
-        <v>11.38500022888184</v>
+        <v>11.30469751358032</v>
       </c>
       <c r="G27" t="n">
-        <v>13.80435609817505</v>
+        <v>12.12259650230408</v>
       </c>
       <c r="H27" t="n">
-        <v>11.48726797103882</v>
+        <v>11.86884546279907</v>
       </c>
       <c r="I27" t="n">
-        <v>15.22022604942322</v>
+        <v>11.47727251052856</v>
       </c>
       <c r="J27" t="n">
-        <v>11.1331250667572</v>
+        <v>11.9361298084259</v>
       </c>
       <c r="K27" t="n">
-        <v>15.32946944236755</v>
+        <v>11.81242680549622</v>
       </c>
       <c r="L27" t="n">
-        <v>12.6807555437088</v>
+        <v>12.18463623523712</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>16.07209873199463</v>
+        <v>11.23737239837646</v>
       </c>
       <c r="C28" t="n">
-        <v>10.66134715080261</v>
+        <v>11.64235329627991</v>
       </c>
       <c r="D28" t="n">
-        <v>11.28026843070984</v>
+        <v>11.85481333732605</v>
       </c>
       <c r="E28" t="n">
-        <v>11.05283117294312</v>
+        <v>12.30620908737183</v>
       </c>
       <c r="F28" t="n">
-        <v>10.54818367958069</v>
+        <v>10.63492441177368</v>
       </c>
       <c r="G28" t="n">
-        <v>15.41621613502502</v>
+        <v>10.63493347167969</v>
       </c>
       <c r="H28" t="n">
-        <v>13.55148267745972</v>
+        <v>10.68829536437988</v>
       </c>
       <c r="I28" t="n">
-        <v>11.40443563461304</v>
+        <v>11.22445726394653</v>
       </c>
       <c r="J28" t="n">
-        <v>11.23145413398743</v>
+        <v>12.21475601196289</v>
       </c>
       <c r="K28" t="n">
-        <v>10.94910645484924</v>
+        <v>10.49078345298767</v>
       </c>
       <c r="L28" t="n">
-        <v>12.21674242019653</v>
+        <v>11.29288980960846</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>9.135235071182251</v>
+        <v>10.60040593147278</v>
       </c>
       <c r="C29" t="n">
-        <v>10.26288819313049</v>
+        <v>13.12035322189331</v>
       </c>
       <c r="D29" t="n">
-        <v>9.846477031707764</v>
+        <v>12.1110155582428</v>
       </c>
       <c r="E29" t="n">
-        <v>15.01820349693298</v>
+        <v>10.28079557418823</v>
       </c>
       <c r="F29" t="n">
-        <v>10.11375665664673</v>
+        <v>10.56302762031555</v>
       </c>
       <c r="G29" t="n">
-        <v>15.58435988426208</v>
+        <v>11.16945886611938</v>
       </c>
       <c r="H29" t="n">
-        <v>9.769628763198853</v>
+        <v>9.941170692443848</v>
       </c>
       <c r="I29" t="n">
-        <v>13.9559371471405</v>
+        <v>10.96896505355835</v>
       </c>
       <c r="J29" t="n">
-        <v>10.10179948806763</v>
+        <v>12.25410151481628</v>
       </c>
       <c r="K29" t="n">
-        <v>9.417048454284668</v>
+        <v>10.36766195297241</v>
       </c>
       <c r="L29" t="n">
-        <v>11.3205334186554</v>
+        <v>11.1376955986023</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>10.96563792228699</v>
+        <v>11.91094040870667</v>
       </c>
       <c r="C30" t="n">
-        <v>11.43689322471619</v>
+        <v>11.70966768264771</v>
       </c>
       <c r="D30" t="n">
-        <v>10.58954572677612</v>
+        <v>14.10483503341675</v>
       </c>
       <c r="E30" t="n">
-        <v>13.93097758293152</v>
+        <v>10.62108588218689</v>
       </c>
       <c r="F30" t="n">
-        <v>17.50644588470459</v>
+        <v>11.41531825065613</v>
       </c>
       <c r="G30" t="n">
-        <v>11.76787447929382</v>
+        <v>16.78834295272827</v>
       </c>
       <c r="H30" t="n">
-        <v>15.22638058662415</v>
+        <v>15.60594701766968</v>
       </c>
       <c r="I30" t="n">
-        <v>10.5660285949707</v>
+        <v>11.34014487266541</v>
       </c>
       <c r="J30" t="n">
-        <v>14.92169284820557</v>
+        <v>14.36561393737793</v>
       </c>
       <c r="K30" t="n">
-        <v>16.5554575920105</v>
+        <v>15.24732398986816</v>
       </c>
       <c r="L30" t="n">
-        <v>13.34669344425201</v>
+        <v>13.31092200279236</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>11.10515117645264</v>
+        <v>19.38605952262878</v>
       </c>
       <c r="C31" t="n">
-        <v>16.36044144630432</v>
+        <v>11.65219855308533</v>
       </c>
       <c r="D31" t="n">
-        <v>14.58156681060791</v>
+        <v>12.4566650390625</v>
       </c>
       <c r="E31" t="n">
-        <v>11.41834998130798</v>
+        <v>11.43629431724548</v>
       </c>
       <c r="F31" t="n">
-        <v>11.24375581741333</v>
+        <v>12.24415469169617</v>
       </c>
       <c r="G31" t="n">
-        <v>15.1640613079071</v>
+        <v>14.35858559608459</v>
       </c>
       <c r="H31" t="n">
-        <v>11.45229649543762</v>
+        <v>11.18738746643066</v>
       </c>
       <c r="I31" t="n">
-        <v>11.52418303489685</v>
+        <v>11.85321640968323</v>
       </c>
       <c r="J31" t="n">
-        <v>11.62837219238281</v>
+        <v>15.1476583480835</v>
       </c>
       <c r="K31" t="n">
-        <v>17.80316758155823</v>
+        <v>10.98890256881714</v>
       </c>
       <c r="L31" t="n">
-        <v>13.22813458442688</v>
+        <v>13.07111225128174</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>10.54813885688782</v>
+        <v>11.2289035320282</v>
       </c>
       <c r="C32" t="n">
-        <v>11.38946533203125</v>
+        <v>10.4189076423645</v>
       </c>
       <c r="D32" t="n">
-        <v>18.98693037033081</v>
+        <v>11.32506656646729</v>
       </c>
       <c r="E32" t="n">
-        <v>12.07027459144592</v>
+        <v>10.69070100784302</v>
       </c>
       <c r="F32" t="n">
-        <v>11.23796105384827</v>
+        <v>11.53051495552063</v>
       </c>
       <c r="G32" t="n">
-        <v>10.87225294113159</v>
+        <v>11.05923128128052</v>
       </c>
       <c r="H32" t="n">
-        <v>14.91024470329285</v>
+        <v>10.91710519790649</v>
       </c>
       <c r="I32" t="n">
-        <v>11.41777515411377</v>
+        <v>11.11762809753418</v>
       </c>
       <c r="J32" t="n">
-        <v>14.4875910282135</v>
+        <v>11.76647329330444</v>
       </c>
       <c r="K32" t="n">
-        <v>14.82322478294373</v>
+        <v>11.60291171073914</v>
       </c>
       <c r="L32" t="n">
-        <v>13.07438588142395</v>
+        <v>11.16574432849884</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>11.5042519569397</v>
+        <v>12.27881622314453</v>
       </c>
       <c r="C33" t="n">
-        <v>11.40051460266113</v>
+        <v>12.47775173187256</v>
       </c>
       <c r="D33" t="n">
-        <v>17.00072622299194</v>
+        <v>11.46579360961914</v>
       </c>
       <c r="E33" t="n">
-        <v>14.16440629959106</v>
+        <v>11.60643696784973</v>
       </c>
       <c r="F33" t="n">
-        <v>11.58249640464783</v>
+        <v>12.93358135223389</v>
       </c>
       <c r="G33" t="n">
-        <v>11.49077367782593</v>
+        <v>11.57303476333618</v>
       </c>
       <c r="H33" t="n">
-        <v>11.2214572429657</v>
+        <v>12.92260837554932</v>
       </c>
       <c r="I33" t="n">
-        <v>12.18498754501343</v>
+        <v>14.61578440666199</v>
       </c>
       <c r="J33" t="n">
-        <v>11.17205476760864</v>
+        <v>11.59946465492249</v>
       </c>
       <c r="K33" t="n">
-        <v>11.0040237903595</v>
+        <v>12.8205554485321</v>
       </c>
       <c r="L33" t="n">
-        <v>12.27256925106049</v>
+        <v>12.42938275337219</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>10.99399948120117</v>
+        <v>11.05704069137573</v>
       </c>
       <c r="C34" t="n">
-        <v>11.20947980880737</v>
+        <v>12.70219087600708</v>
       </c>
       <c r="D34" t="n">
-        <v>11.04786252975464</v>
+        <v>10.32319355010986</v>
       </c>
       <c r="E34" t="n">
-        <v>10.75808262825012</v>
+        <v>10.96458435058594</v>
       </c>
       <c r="F34" t="n">
-        <v>12.51662492752075</v>
+        <v>11.27376341819763</v>
       </c>
       <c r="G34" t="n">
-        <v>10.46985840797424</v>
+        <v>10.79102039337158</v>
       </c>
       <c r="H34" t="n">
-        <v>13.38844680786133</v>
+        <v>12.27823328971863</v>
       </c>
       <c r="I34" t="n">
-        <v>14.25034475326538</v>
+        <v>10.61572623252869</v>
       </c>
       <c r="J34" t="n">
-        <v>10.57905149459839</v>
+        <v>10.59480786323547</v>
       </c>
       <c r="K34" t="n">
-        <v>10.52669501304626</v>
+        <v>11.86297369003296</v>
       </c>
       <c r="L34" t="n">
-        <v>11.57404458522797</v>
+        <v>11.24635343551636</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>11.25834393501282</v>
+        <v>15.35141849517822</v>
       </c>
       <c r="C35" t="n">
-        <v>11.68873500823975</v>
+        <v>11.36807680130005</v>
       </c>
       <c r="D35" t="n">
-        <v>12.09476041793823</v>
+        <v>10.84438276290894</v>
       </c>
       <c r="E35" t="n">
-        <v>10.92068362236023</v>
+        <v>13.199866771698</v>
       </c>
       <c r="F35" t="n">
-        <v>18.21512055397034</v>
+        <v>14.3923168182373</v>
       </c>
       <c r="G35" t="n">
-        <v>11.19950532913208</v>
+        <v>12.35409021377563</v>
       </c>
       <c r="H35" t="n">
-        <v>12.34306263923645</v>
+        <v>11.11420369148254</v>
       </c>
       <c r="I35" t="n">
-        <v>11.84684777259827</v>
+        <v>11.59249663352966</v>
       </c>
       <c r="J35" t="n">
-        <v>12.64280414581299</v>
+        <v>11.7476692199707</v>
       </c>
       <c r="K35" t="n">
-        <v>11.02495098114014</v>
+        <v>12.69241237640381</v>
       </c>
       <c r="L35" t="n">
-        <v>12.32348144054413</v>
+        <v>12.46569337844849</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>11.27923893928528</v>
+        <v>11.86876893043518</v>
       </c>
       <c r="C36" t="n">
-        <v>12.23782444000244</v>
+        <v>12.94653010368347</v>
       </c>
       <c r="D36" t="n">
-        <v>11.14714670181274</v>
+        <v>11.47631144523621</v>
       </c>
       <c r="E36" t="n">
-        <v>12.2919807434082</v>
+        <v>13.08467650413513</v>
       </c>
       <c r="F36" t="n">
-        <v>10.15707755088806</v>
+        <v>11.43486380577087</v>
       </c>
       <c r="G36" t="n">
-        <v>11.04479384422302</v>
+        <v>11.38503456115723</v>
       </c>
       <c r="H36" t="n">
-        <v>11.51606488227844</v>
+        <v>11.30971550941467</v>
       </c>
       <c r="I36" t="n">
-        <v>11.56298685073853</v>
+        <v>10.7650842666626</v>
       </c>
       <c r="J36" t="n">
-        <v>12.69099116325378</v>
+        <v>13.31959199905396</v>
       </c>
       <c r="K36" t="n">
-        <v>11.36442470550537</v>
+        <v>11.39000105857849</v>
       </c>
       <c r="L36" t="n">
-        <v>11.52925298213959</v>
+        <v>11.89805781841278</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>10.15407490730286</v>
+        <v>10.96559953689575</v>
       </c>
       <c r="C37" t="n">
-        <v>11.52154326438904</v>
+        <v>11.15109801292419</v>
       </c>
       <c r="D37" t="n">
-        <v>10.65479779243469</v>
+        <v>11.67376804351807</v>
       </c>
       <c r="E37" t="n">
-        <v>10.47962522506714</v>
+        <v>11.68625330924988</v>
       </c>
       <c r="F37" t="n">
-        <v>10.62192487716675</v>
+        <v>11.40096735954285</v>
       </c>
       <c r="G37" t="n">
-        <v>11.43564534187317</v>
+        <v>11.21741485595703</v>
       </c>
       <c r="H37" t="n">
-        <v>11.32601022720337</v>
+        <v>11.31069827079773</v>
       </c>
       <c r="I37" t="n">
-        <v>12.0001425743103</v>
+        <v>11.23142433166504</v>
       </c>
       <c r="J37" t="n">
-        <v>11.6843409538269</v>
+        <v>12.44231867790222</v>
       </c>
       <c r="K37" t="n">
-        <v>13.37201380729675</v>
+        <v>11.30569767951965</v>
       </c>
       <c r="L37" t="n">
-        <v>11.3250118970871</v>
+        <v>11.43852400779724</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>11.27229619026184</v>
+        <v>11.361576795578</v>
       </c>
       <c r="C38" t="n">
-        <v>11.08232283592224</v>
+        <v>11.10422897338867</v>
       </c>
       <c r="D38" t="n">
-        <v>10.93370771408081</v>
+        <v>16.75185346603394</v>
       </c>
       <c r="E38" t="n">
-        <v>12.11168217658997</v>
+        <v>11.93416905403137</v>
       </c>
       <c r="F38" t="n">
-        <v>13.11506962776184</v>
+        <v>10.51972794532776</v>
       </c>
       <c r="G38" t="n">
-        <v>10.38802576065063</v>
+        <v>11.08772921562195</v>
       </c>
       <c r="H38" t="n">
-        <v>12.52958154678345</v>
+        <v>13.85978603363037</v>
       </c>
       <c r="I38" t="n">
-        <v>15.02973031997681</v>
+        <v>10.78799390792847</v>
       </c>
       <c r="J38" t="n">
-        <v>10.93867087364197</v>
+        <v>11.8681845664978</v>
       </c>
       <c r="K38" t="n">
-        <v>10.9601001739502</v>
+        <v>11.66322708129883</v>
       </c>
       <c r="L38" t="n">
-        <v>11.83611872196198</v>
+        <v>12.09384770393372</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>10.48230528831482</v>
+        <v>9.749155759811401</v>
       </c>
       <c r="C39" t="n">
-        <v>10.39454412460327</v>
+        <v>11.08767628669739</v>
       </c>
       <c r="D39" t="n">
-        <v>9.6364905834198</v>
+        <v>10.15408492088318</v>
       </c>
       <c r="E39" t="n">
-        <v>13.96144723892212</v>
+        <v>11.25273942947388</v>
       </c>
       <c r="F39" t="n">
-        <v>9.899762153625488</v>
+        <v>10.38900566101074</v>
       </c>
       <c r="G39" t="n">
-        <v>10.01350903511047</v>
+        <v>9.708283424377441</v>
       </c>
       <c r="H39" t="n">
-        <v>10.29928660392761</v>
+        <v>10.32962346076965</v>
       </c>
       <c r="I39" t="n">
-        <v>10.51570868492126</v>
+        <v>10.20344519615173</v>
       </c>
       <c r="J39" t="n">
-        <v>10.24391794204712</v>
+        <v>12.05430126190186</v>
       </c>
       <c r="K39" t="n">
-        <v>13.78505873680115</v>
+        <v>10.50776052474976</v>
       </c>
       <c r="L39" t="n">
-        <v>10.92320303916931</v>
+        <v>10.5436075925827</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>11.56143260002136</v>
+        <v>12.67635416984558</v>
       </c>
       <c r="C40" t="n">
-        <v>13.33679723739624</v>
+        <v>11.93208837509155</v>
       </c>
       <c r="D40" t="n">
-        <v>15.12513494491577</v>
+        <v>11.75105667114258</v>
       </c>
       <c r="E40" t="n">
-        <v>13.03413844108582</v>
+        <v>14.69854140281677</v>
       </c>
       <c r="F40" t="n">
-        <v>13.41313123703003</v>
+        <v>12.81092548370361</v>
       </c>
       <c r="G40" t="n">
-        <v>11.71007037162781</v>
+        <v>13.61032748222351</v>
       </c>
       <c r="H40" t="n">
-        <v>10.94203305244446</v>
+        <v>13.57792782783508</v>
       </c>
       <c r="I40" t="n">
-        <v>12.92585253715515</v>
+        <v>12.4517650604248</v>
       </c>
       <c r="J40" t="n">
-        <v>11.72605061531067</v>
+        <v>11.33465003967285</v>
       </c>
       <c r="K40" t="n">
-        <v>11.43825936317444</v>
+        <v>12.3034040927887</v>
       </c>
       <c r="L40" t="n">
-        <v>12.52129004001617</v>
+        <v>12.7147040605545</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>12.23391270637512</v>
+        <v>12.77894234657288</v>
       </c>
       <c r="C41" t="n">
-        <v>10.07332396507263</v>
+        <v>14.78434085845947</v>
       </c>
       <c r="D41" t="n">
-        <v>12.80840015411377</v>
+        <v>9.819496631622314</v>
       </c>
       <c r="E41" t="n">
-        <v>13.31359815597534</v>
+        <v>10.0708475112915</v>
       </c>
       <c r="F41" t="n">
-        <v>13.07768893241882</v>
+        <v>10.71323084831238</v>
       </c>
       <c r="G41" t="n">
-        <v>13.11909055709839</v>
+        <v>12.79290819168091</v>
       </c>
       <c r="H41" t="n">
-        <v>11.37115836143494</v>
+        <v>9.955646753311157</v>
       </c>
       <c r="I41" t="n">
-        <v>10.81450605392456</v>
+        <v>11.16604804992676</v>
       </c>
       <c r="J41" t="n">
-        <v>9.698342800140381</v>
+        <v>10.55566167831421</v>
       </c>
       <c r="K41" t="n">
-        <v>9.240985155105591</v>
+        <v>12.90715956687927</v>
       </c>
       <c r="L41" t="n">
-        <v>11.57510068416595</v>
+        <v>11.55442824363709</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>11.18503046035767</v>
+        <v>11.97648787498474</v>
       </c>
       <c r="C42" t="n">
-        <v>12.22294116020203</v>
+        <v>10.70923566818237</v>
       </c>
       <c r="D42" t="n">
-        <v>12.33907508850098</v>
+        <v>11.59694623947144</v>
       </c>
       <c r="E42" t="n">
-        <v>12.39149212837219</v>
+        <v>14.58583855628967</v>
       </c>
       <c r="F42" t="n">
-        <v>11.528160572052</v>
+        <v>11.87081027030945</v>
       </c>
       <c r="G42" t="n">
-        <v>11.61640381813049</v>
+        <v>14.86567497253418</v>
       </c>
       <c r="H42" t="n">
-        <v>10.89123225212097</v>
+        <v>12.29369425773621</v>
       </c>
       <c r="I42" t="n">
-        <v>12.14806962013245</v>
+        <v>14.79729175567627</v>
       </c>
       <c r="J42" t="n">
-        <v>13.59987425804138</v>
+        <v>13.66721510887146</v>
       </c>
       <c r="K42" t="n">
-        <v>11.36808037757874</v>
+        <v>12.78344774246216</v>
       </c>
       <c r="L42" t="n">
-        <v>11.92903597354889</v>
+        <v>12.91466424465179</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>15.14292216300964</v>
+        <v>11.86978530883789</v>
       </c>
       <c r="C43" t="n">
-        <v>10.98304104804993</v>
+        <v>11.90519595146179</v>
       </c>
       <c r="D43" t="n">
-        <v>10.49225854873657</v>
+        <v>16.21968460083008</v>
       </c>
       <c r="E43" t="n">
-        <v>12.25778889656067</v>
+        <v>11.1252167224884</v>
       </c>
       <c r="F43" t="n">
-        <v>13.12904715538025</v>
+        <v>11.79144287109375</v>
       </c>
       <c r="G43" t="n">
-        <v>14.37541747093201</v>
+        <v>12.12957882881165</v>
       </c>
       <c r="H43" t="n">
-        <v>10.57057046890259</v>
+        <v>12.56898808479309</v>
       </c>
       <c r="I43" t="n">
-        <v>11.54312491416931</v>
+        <v>11.52219557762146</v>
       </c>
       <c r="J43" t="n">
-        <v>12.15417814254761</v>
+        <v>15.20974183082581</v>
       </c>
       <c r="K43" t="n">
-        <v>13.24128413200378</v>
+        <v>10.99994039535522</v>
       </c>
       <c r="L43" t="n">
-        <v>12.38896329402924</v>
+        <v>12.53417701721191</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>12.40048432350159</v>
+        <v>12.71710777282715</v>
       </c>
       <c r="C44" t="n">
-        <v>14.93053102493286</v>
+        <v>16.37231874465942</v>
       </c>
       <c r="D44" t="n">
-        <v>13.35153245925903</v>
+        <v>12.11661863327026</v>
       </c>
       <c r="E44" t="n">
-        <v>14.79183650016785</v>
+        <v>13.68818330764771</v>
       </c>
       <c r="F44" t="n">
-        <v>14.40034747123718</v>
+        <v>14.30604577064514</v>
       </c>
       <c r="G44" t="n">
-        <v>16.36381673812866</v>
+        <v>11.8767614364624</v>
       </c>
       <c r="H44" t="n">
-        <v>11.85379338264465</v>
+        <v>11.9091637134552</v>
       </c>
       <c r="I44" t="n">
-        <v>12.80168581008911</v>
+        <v>13.68670392036438</v>
       </c>
       <c r="J44" t="n">
-        <v>17.63015270233154</v>
+        <v>12.9824104309082</v>
       </c>
       <c r="K44" t="n">
-        <v>12.19825100898743</v>
+        <v>16.32063508033752</v>
       </c>
       <c r="L44" t="n">
-        <v>14.07224314212799</v>
+        <v>13.59759488105774</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>10.837886095047</v>
+        <v>10.29740691184998</v>
       </c>
       <c r="C45" t="n">
-        <v>12.38679099082947</v>
+        <v>12.12796258926392</v>
       </c>
       <c r="D45" t="n">
-        <v>11.16235566139221</v>
+        <v>10.83380532264709</v>
       </c>
       <c r="E45" t="n">
-        <v>10.10224485397339</v>
+        <v>13.03108501434326</v>
       </c>
       <c r="F45" t="n">
-        <v>12.27729749679565</v>
+        <v>10.89675450325012</v>
       </c>
       <c r="G45" t="n">
-        <v>10.51273274421692</v>
+        <v>10.0374550819397</v>
       </c>
       <c r="H45" t="n">
-        <v>11.83788371086121</v>
+        <v>10.77305197715759</v>
       </c>
       <c r="I45" t="n">
-        <v>10.51374483108521</v>
+        <v>12.81338620185852</v>
       </c>
       <c r="J45" t="n">
-        <v>11.52621245384216</v>
+        <v>9.920256853103638</v>
       </c>
       <c r="K45" t="n">
-        <v>11.92548966407776</v>
+        <v>10.88774800300598</v>
       </c>
       <c r="L45" t="n">
-        <v>11.3082638502121</v>
+        <v>11.16189124584198</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>12.11818265914917</v>
+        <v>12.17113018035889</v>
       </c>
       <c r="C46" t="n">
-        <v>12.29071521759033</v>
+        <v>12.25764012336731</v>
       </c>
       <c r="D46" t="n">
-        <v>11.90419864654541</v>
+        <v>15.16509985923767</v>
       </c>
       <c r="E46" t="n">
-        <v>12.26176977157593</v>
+        <v>12.26091027259827</v>
       </c>
       <c r="F46" t="n">
-        <v>13.37698149681091</v>
+        <v>11.438227891922</v>
       </c>
       <c r="G46" t="n">
-        <v>16.18760275840759</v>
+        <v>14.85586500167847</v>
       </c>
       <c r="H46" t="n">
-        <v>11.5046124458313</v>
+        <v>13.20613479614258</v>
       </c>
       <c r="I46" t="n">
-        <v>11.71408462524414</v>
+        <v>12.45709276199341</v>
       </c>
       <c r="J46" t="n">
-        <v>13.84697651863098</v>
+        <v>16.21228432655334</v>
       </c>
       <c r="K46" t="n">
-        <v>10.92408490180969</v>
+        <v>13.96771883964539</v>
       </c>
       <c r="L46" t="n">
-        <v>12.61292090415955</v>
+        <v>13.39921040534973</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>14.34216594696045</v>
+        <v>11.68614625930786</v>
       </c>
       <c r="C47" t="n">
-        <v>12.11699986457825</v>
+        <v>11.70258259773254</v>
       </c>
       <c r="D47" t="n">
-        <v>10.91211724281311</v>
+        <v>13.44003462791443</v>
       </c>
       <c r="E47" t="n">
-        <v>11.15592193603516</v>
+        <v>10.98793482780457</v>
       </c>
       <c r="F47" t="n">
-        <v>13.84097599983215</v>
+        <v>14.39457869529724</v>
       </c>
       <c r="G47" t="n">
-        <v>10.08026933670044</v>
+        <v>11.54050779342651</v>
       </c>
       <c r="H47" t="n">
-        <v>11.55742263793945</v>
+        <v>12.39180874824524</v>
       </c>
       <c r="I47" t="n">
-        <v>11.80630254745483</v>
+        <v>12.95856785774231</v>
       </c>
       <c r="J47" t="n">
-        <v>13.147296667099</v>
+        <v>15.78131985664368</v>
       </c>
       <c r="K47" t="n">
-        <v>10.80291986465454</v>
+        <v>11.6837329864502</v>
       </c>
       <c r="L47" t="n">
-        <v>11.97623920440674</v>
+        <v>12.65672142505646</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>12.78075361251831</v>
+        <v>11.97749853134155</v>
       </c>
       <c r="C48" t="n">
-        <v>11.95748138427734</v>
+        <v>12.12859988212585</v>
       </c>
       <c r="D48" t="n">
-        <v>11.77988505363464</v>
+        <v>11.02793741226196</v>
       </c>
       <c r="E48" t="n">
-        <v>12.66858887672424</v>
+        <v>11.11718201637268</v>
       </c>
       <c r="F48" t="n">
-        <v>11.30197429656982</v>
+        <v>11.44687175750732</v>
       </c>
       <c r="G48" t="n">
-        <v>11.84184885025024</v>
+        <v>12.74105429649353</v>
       </c>
       <c r="H48" t="n">
-        <v>11.88376498222351</v>
+        <v>13.2012026309967</v>
       </c>
       <c r="I48" t="n">
-        <v>11.90625143051147</v>
+        <v>11.65868401527405</v>
       </c>
       <c r="J48" t="n">
-        <v>12.71314764022827</v>
+        <v>11.47815465927124</v>
       </c>
       <c r="K48" t="n">
-        <v>12.50964689254761</v>
+        <v>12.59326267242432</v>
       </c>
       <c r="L48" t="n">
-        <v>12.13433430194855</v>
+        <v>11.93704478740692</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>10.47131562232971</v>
+        <v>11.31507039070129</v>
       </c>
       <c r="C49" t="n">
-        <v>11.42888855934143</v>
+        <v>11.54350304603577</v>
       </c>
       <c r="D49" t="n">
-        <v>12.10268640518188</v>
+        <v>14.80550384521484</v>
       </c>
       <c r="E49" t="n">
-        <v>10.81044816970825</v>
+        <v>13.78274345397949</v>
       </c>
       <c r="F49" t="n">
-        <v>10.91268825531006</v>
+        <v>10.91108751296997</v>
       </c>
       <c r="G49" t="n">
-        <v>11.2967803478241</v>
+        <v>11.19398164749146</v>
       </c>
       <c r="H49" t="n">
-        <v>11.7435827255249</v>
+        <v>13.90932965278625</v>
       </c>
       <c r="I49" t="n">
-        <v>11.76850581169128</v>
+        <v>12.44030141830444</v>
       </c>
       <c r="J49" t="n">
-        <v>12.54589676856995</v>
+        <v>11.08576273918152</v>
       </c>
       <c r="K49" t="n">
-        <v>11.41960549354553</v>
+        <v>11.4209201335907</v>
       </c>
       <c r="L49" t="n">
-        <v>11.45003981590271</v>
+        <v>12.24082038402557</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>11.2971043586731</v>
+        <v>11.04390549659729</v>
       </c>
       <c r="C50" t="n">
-        <v>11.37391114234924</v>
+        <v>13.98788499832153</v>
       </c>
       <c r="D50" t="n">
-        <v>11.81926560401917</v>
+        <v>11.57852554321289</v>
       </c>
       <c r="E50" t="n">
-        <v>10.97652244567871</v>
+        <v>10.72122955322266</v>
       </c>
       <c r="F50" t="n">
-        <v>11.42634582519531</v>
+        <v>10.84141206741333</v>
       </c>
       <c r="G50" t="n">
-        <v>10.73256707191467</v>
+        <v>11.09131336212158</v>
       </c>
       <c r="H50" t="n">
-        <v>10.38050866127014</v>
+        <v>11.23937654495239</v>
       </c>
       <c r="I50" t="n">
-        <v>11.86069536209106</v>
+        <v>15.37749886512756</v>
       </c>
       <c r="J50" t="n">
-        <v>13.26451206207275</v>
+        <v>12.13501739501953</v>
       </c>
       <c r="K50" t="n">
-        <v>12.19233131408691</v>
+        <v>12.33350896835327</v>
       </c>
       <c r="L50" t="n">
-        <v>11.53237638473511</v>
+        <v>12.0349672794342</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>12.33738040924072</v>
+        <v>11.31720519065857</v>
       </c>
       <c r="C51" t="n">
-        <v>11.07021760940552</v>
+        <v>10.60964822769165</v>
       </c>
       <c r="D51" t="n">
-        <v>10.55656623840332</v>
+        <v>12.59593868255615</v>
       </c>
       <c r="E51" t="n">
-        <v>10.63932752609253</v>
+        <v>10.04845237731934</v>
       </c>
       <c r="F51" t="n">
-        <v>9.986025810241699</v>
+        <v>10.46683645248413</v>
       </c>
       <c r="G51" t="n">
-        <v>11.34498071670532</v>
+        <v>11.39606547355652</v>
       </c>
       <c r="H51" t="n">
-        <v>10.89863705635071</v>
+        <v>10.53210186958313</v>
       </c>
       <c r="I51" t="n">
-        <v>10.19549822807312</v>
+        <v>11.12055087089539</v>
       </c>
       <c r="J51" t="n">
-        <v>12.3463830947876</v>
+        <v>11.82024502754211</v>
       </c>
       <c r="K51" t="n">
-        <v>11.30309629440308</v>
+        <v>11.08632445335388</v>
       </c>
       <c r="L51" t="n">
-        <v>11.06781129837036</v>
+        <v>11.09933686256409</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.0006253528595</v>
+        <v>12.01472731113434</v>
       </c>
       <c r="C52" t="n">
-        <v>12.07635770797729</v>
+        <v>12.23372947692871</v>
       </c>
       <c r="D52" t="n">
-        <v>12.08127828598023</v>
+        <v>12.2061340045929</v>
       </c>
       <c r="E52" t="n">
-        <v>12.30774486064911</v>
+        <v>12.3917547082901</v>
       </c>
       <c r="F52" t="n">
-        <v>12.42162962436676</v>
+        <v>11.69594927310944</v>
       </c>
       <c r="G52" t="n">
-        <v>12.10216187000275</v>
+        <v>12.14322060585022</v>
       </c>
       <c r="H52" t="n">
-        <v>12.20024295806885</v>
+        <v>12.07112334251404</v>
       </c>
       <c r="I52" t="n">
-        <v>12.05810108184814</v>
+        <v>12.16750434875488</v>
       </c>
       <c r="J52" t="n">
-        <v>12.29359669208527</v>
+        <v>12.39145025253296</v>
       </c>
       <c r="K52" t="n">
-        <v>12.2715260219574</v>
+        <v>12.54665467739105</v>
       </c>
       <c r="L52" t="n">
-        <v>12.18132644557953</v>
+        <v>12.18622480010986</v>
       </c>
     </row>
   </sheetData>
